--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,12 +42,6 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -97,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -138,9 +132,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
@@ -151,7 +142,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -521,16 +512,16 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="25.005" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="16" min="2" max="2"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="17" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="15" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="18" min="6" max="6"/>
-    <col width="15.005" bestFit="1" customWidth="1" style="19" min="7" max="7"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="15" min="2" max="2"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="17" min="6" max="6"/>
+    <col width="15.005" bestFit="1" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
@@ -554,7 +545,7 @@
           <t>celular</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>congregacion</t>
         </is>
@@ -571,7 +562,7 @@
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Marcia Lucrecia Lourdes Benitez</t>
         </is>
@@ -581,7 +572,7 @@
           <t>35,450,627</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>marciabenitezll@gmail.com</t>
         </is>
@@ -591,7 +582,7 @@
           <t>3794534177</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -606,7 +597,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Maira Melanie Ailen Benitez</t>
         </is>
@@ -616,7 +607,7 @@
           <t>42,097,841</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>ailenmelbenitez99@gmail.com</t>
         </is>
@@ -626,7 +617,7 @@
           <t>3795366654</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -641,7 +632,7 @@
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Analia Cambiaso</t>
         </is>
@@ -651,7 +642,7 @@
           <t>11,464,195</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
@@ -661,7 +652,7 @@
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -676,7 +667,7 @@
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Anderson da Rocha Fernandes</t>
         </is>
@@ -686,7 +677,7 @@
           <t>95,276,764</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -696,7 +687,7 @@
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -711,7 +702,7 @@
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Juliana Cristina Siqueira Fernandes</t>
         </is>
@@ -721,7 +712,7 @@
           <t>95,276,773</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -731,7 +722,7 @@
           <t>3777238654</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -746,7 +737,7 @@
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Samuel Siqueira Fernandes</t>
         </is>
@@ -756,7 +747,7 @@
           <t>95,279,778</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -766,7 +757,7 @@
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -781,7 +772,7 @@
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Alan Lionel Gonzalez</t>
         </is>
@@ -791,7 +782,7 @@
           <t>48,399,343</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -801,7 +792,7 @@
           <t>3777222734</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -816,7 +807,7 @@
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Valentina Fernandes Siqueira</t>
         </is>
@@ -826,7 +817,7 @@
           <t>54,649,578</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -836,7 +827,7 @@
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -851,7 +842,7 @@
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Vera Valeria Andrea</t>
         </is>
@@ -861,7 +852,7 @@
           <t>37,394,518</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>valeria_694202@hotmail.com</t>
         </is>
@@ -871,7 +862,7 @@
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
@@ -886,7 +877,7 @@
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Silvero Augusto Andres</t>
         </is>
@@ -896,7 +887,7 @@
           <t>36,674,838</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>augusto_la32@hotmail.com</t>
         </is>
@@ -906,7 +897,7 @@
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
@@ -921,7 +912,7 @@
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Jonatan Ariel Gonzalez</t>
         </is>
@@ -931,7 +922,7 @@
           <t>35,035,210</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Jonidespertad18@gmail.com</t>
         </is>
@@ -941,7 +932,7 @@
           <t>3777531414</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -956,7 +947,7 @@
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Melina Isabel Barbona</t>
         </is>
@@ -966,7 +957,7 @@
           <t>36,445,555</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>jonidespertad18@gmail.com</t>
         </is>
@@ -976,7 +967,7 @@
           <t>3777691836</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -991,7 +982,7 @@
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Abigail Martinez</t>
         </is>
@@ -1001,7 +992,7 @@
           <t>49,666,988</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>martineznahirabigail@gmail.com</t>
         </is>
@@ -1011,7 +1002,7 @@
           <t>3794096406</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1028,7 +1019,7 @@
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Gustavo Escobar</t>
         </is>
@@ -1038,7 +1029,7 @@
           <t>95,259,056</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
@@ -1048,7 +1039,7 @@
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1065,7 +1056,7 @@
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Ximena Robledo</t>
         </is>
@@ -1075,7 +1066,7 @@
           <t>5,321,660</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
@@ -1085,7 +1076,7 @@
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1102,7 +1093,7 @@
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Lourdes Coronek</t>
         </is>
@@ -1112,7 +1103,7 @@
           <t>95,216,658</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
@@ -1122,7 +1113,7 @@
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1139,7 +1130,7 @@
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Chapo Noelia Adriana</t>
         </is>
@@ -1149,7 +1140,7 @@
           <t>29,881,151</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Noeliaadrianachapo@gmail.com</t>
         </is>
@@ -1159,7 +1150,7 @@
           <t>3718545378</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1176,7 +1167,7 @@
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Jorge Jose Baez</t>
         </is>
@@ -1186,11 +1177,11 @@
           <t>28,420,407</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n"/>
+      <c r="C19" s="14" t="n"/>
       <c r="D19" s="12" t="n">
         <v>3718546293</v>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1207,7 +1198,7 @@
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Emanuel Baukloh</t>
         </is>
@@ -1217,7 +1208,7 @@
           <t>41,177,151</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>emanuelbaukloh@gmail.com</t>
         </is>
@@ -1227,7 +1218,7 @@
           <t>3718458439</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1244,7 +1235,7 @@
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Francini Gustavo Daniel</t>
         </is>
@@ -1254,7 +1245,7 @@
           <t>37,884,991</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>gusfrancini@gmail.com</t>
         </is>
@@ -1264,7 +1255,7 @@
           <t>3794526768</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1281,7 +1272,7 @@
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Sotelo Maria Laura</t>
         </is>
@@ -1291,7 +1282,7 @@
           <t>38,876,535</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>sotelolaura209@gmail.com</t>
         </is>
@@ -1301,7 +1292,7 @@
           <t>3794235747</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1318,7 +1309,7 @@
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Abril Steinle</t>
         </is>
@@ -1326,7 +1317,7 @@
       <c r="B23" s="7" t="n">
         <v>43066068</v>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Steinleabril13@gmail.com</t>
         </is>
@@ -1336,7 +1327,7 @@
           <t>3794005300</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1353,7 +1344,7 @@
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Maria Daniela Del Buono</t>
         </is>
@@ -1363,7 +1354,7 @@
           <t>31,849,062</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
@@ -1373,7 +1364,7 @@
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1388,7 +1379,7 @@
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Agustina Daniela Mantaras</t>
         </is>
@@ -1398,7 +1389,7 @@
           <t>46,785,165</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>agustinamantaras8@gmail.com</t>
         </is>
@@ -1408,7 +1399,7 @@
           <t>3764740347</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1423,7 +1414,7 @@
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Hector Luis Ayala</t>
         </is>
@@ -1433,7 +1424,7 @@
           <t>21,855,255</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
@@ -1443,7 +1434,7 @@
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1456,7 +1447,7 @@
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Irma Vallejos</t>
         </is>
@@ -1466,7 +1457,7 @@
           <t>14,663,815</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
@@ -1476,7 +1467,7 @@
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1489,7 +1480,7 @@
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Virginia Riveros</t>
         </is>
@@ -1499,7 +1490,7 @@
           <t>29,223,709</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
@@ -1509,7 +1500,7 @@
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
@@ -1522,7 +1513,7 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Florencia Cabral</t>
         </is>
@@ -1532,7 +1523,7 @@
           <t>51,520,144</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
@@ -1542,7 +1533,7 @@
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
@@ -1555,7 +1546,7 @@
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Debora Raquel Amarilla González</t>
         </is>
@@ -1565,7 +1556,7 @@
           <t>43,532,913</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>deboradrag15@gmail.com</t>
         </is>
@@ -1575,7 +1566,7 @@
           <t>3794023063</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>Voz que Clama</t>
         </is>
@@ -1588,7 +1579,7 @@
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Cabral Fernando R. Adrian</t>
         </is>
@@ -1598,13 +1589,17 @@
           <t>28,397,653</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>frac007@hotmail.com</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>54 9 362 4557191</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Pacto de restauracion</t>
         </is>
@@ -1617,7 +1612,7 @@
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Victoria Valentina Ayala</t>
         </is>
@@ -1627,7 +1622,7 @@
           <t>46,718,239</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
@@ -1637,7 +1632,7 @@
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1650,7 +1645,7 @@
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Yeniffer Silvera Suárez</t>
         </is>
@@ -1660,7 +1655,7 @@
           <t>53,483,881</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>yensilsuar13@gmail.com</t>
         </is>
@@ -1670,7 +1665,7 @@
           <t>+598 094 135 946</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1683,7 +1678,7 @@
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Renzo Acosta</t>
         </is>
@@ -1693,7 +1688,7 @@
           <t>54,848,640</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>acostarenzo975@gmail.com</t>
         </is>
@@ -1703,7 +1698,7 @@
           <t>+598 94 930 080</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1716,7 +1711,7 @@
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Gabriela Coronel</t>
         </is>
@@ -1726,7 +1721,7 @@
           <t>53,589,489</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>Sandracoronel.07@gmail.com</t>
         </is>
@@ -1736,7 +1731,7 @@
           <t>+598 93 640 559</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
@@ -1749,7 +1744,7 @@
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Nahuel Acosta</t>
         </is>
@@ -1759,7 +1754,7 @@
           <t>54,015,825</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Nahuel_acosta12@hotmail.com</t>
         </is>
@@ -1769,7 +1764,7 @@
           <t>+598 94 805 438</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
@@ -1782,7 +1777,7 @@
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Noemí Roldán</t>
         </is>
@@ -1792,7 +1787,7 @@
           <t>56,349,232</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>noeroldan545@gmail.com</t>
         </is>
@@ -1802,7 +1797,7 @@
           <t>+598 092237179</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1815,7 +1810,7 @@
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Marcelo Andres Pirez Aquino</t>
         </is>
@@ -1825,7 +1820,7 @@
           <t>48,841,472</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>marcelopirez459@gmail.com</t>
         </is>
@@ -1835,7 +1830,7 @@
           <t>+598 096401066</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1848,7 +1843,7 @@
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Rosa Vallejos</t>
         </is>
@@ -1858,7 +1853,7 @@
           <t>12,687,300</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>Rosavallejos1805@gamail.com</t>
         </is>
@@ -1868,7 +1863,7 @@
           <t>3624-283862</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Pacto de restauración central</t>
         </is>
@@ -1881,7 +1876,7 @@
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Yohana Belen Galarza</t>
         </is>
@@ -1891,7 +1886,7 @@
           <t>40,281,097</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>hous1516@gmail.com</t>
         </is>
@@ -1901,7 +1896,7 @@
           <t>3756596984</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Centro Cristiano para las Familias</t>
         </is>
@@ -1914,7 +1909,7 @@
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Gisela Davalos</t>
         </is>
@@ -1924,7 +1919,7 @@
           <t>36,317,286</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>gise130513@gmail.com</t>
         </is>
@@ -1934,13 +1929,232 @@
           <t>+54 9 3794 80-7731</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F41" s="14" t="n"/>
+      <c r="F41" s="5" t="n"/>
       <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Matías Benjamín Velázquez Acuña</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>47,539,002</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>benjavel06@gmail.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3794280284</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Iglesia Bautista del Amor</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Romina Noelia Acuña</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>32,880,155</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ronoeliaacuna@gmail.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3795033741</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Iglesia Bautista del Amor</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nadia Montenegro</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>32,061,700</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>nadiaemilia5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3468-411458</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Candela Basualdo Freytes</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>46,770,578</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>candebasfrey@gmail.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3468642321</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Arnold Tomas Pavon</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>44,296,431</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>candebasfrey@gmail.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3468642321</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gustavo Scholles</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gustavo123scholles@gmail.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>+54 9 3754 41-6387</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Yolanda Alicia Reyes</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20,312,303</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Reyesyolanda5798@gmail.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3794-976944</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>

--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -132,20 +132,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,16 +524,16 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="25.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="15" min="2" max="2"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="17" min="6" max="6"/>
-    <col width="15.005" bestFit="1" customWidth="1" style="18" min="7" max="7"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="19" min="2" max="2"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="18" min="3" max="3"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="18" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="21" min="6" max="6"/>
+    <col width="15.005" bestFit="1" customWidth="1" style="22" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
@@ -545,7 +557,7 @@
           <t>celular</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>congregacion</t>
         </is>
@@ -562,7 +574,7 @@
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Marcia Lucrecia Lourdes Benitez</t>
         </is>
@@ -572,7 +584,7 @@
           <t>35,450,627</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>marciabenitezll@gmail.com</t>
         </is>
@@ -582,7 +594,7 @@
           <t>3794534177</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -597,7 +609,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Maira Melanie Ailen Benitez</t>
         </is>
@@ -607,7 +619,7 @@
           <t>42,097,841</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>ailenmelbenitez99@gmail.com</t>
         </is>
@@ -617,7 +629,7 @@
           <t>3795366654</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -632,7 +644,7 @@
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Analia Cambiaso</t>
         </is>
@@ -642,7 +654,7 @@
           <t>11,464,195</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
@@ -652,7 +664,7 @@
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -667,7 +679,7 @@
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Anderson da Rocha Fernandes</t>
         </is>
@@ -677,7 +689,7 @@
           <t>95,276,764</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -687,7 +699,7 @@
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -702,7 +714,7 @@
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Juliana Cristina Siqueira Fernandes</t>
         </is>
@@ -712,7 +724,7 @@
           <t>95,276,773</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -722,7 +734,7 @@
           <t>3777238654</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -737,7 +749,7 @@
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Samuel Siqueira Fernandes</t>
         </is>
@@ -747,7 +759,7 @@
           <t>95,279,778</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -757,7 +769,7 @@
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -772,7 +784,7 @@
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Alan Lionel Gonzalez</t>
         </is>
@@ -782,7 +794,7 @@
           <t>48,399,343</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -792,7 +804,7 @@
           <t>3777222734</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -807,7 +819,7 @@
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Valentina Fernandes Siqueira</t>
         </is>
@@ -817,7 +829,7 @@
           <t>54,649,578</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
@@ -827,7 +839,7 @@
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -842,7 +854,7 @@
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Vera Valeria Andrea</t>
         </is>
@@ -852,7 +864,7 @@
           <t>37,394,518</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>valeria_694202@hotmail.com</t>
         </is>
@@ -862,7 +874,7 @@
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
@@ -877,7 +889,7 @@
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Silvero Augusto Andres</t>
         </is>
@@ -887,7 +899,7 @@
           <t>36,674,838</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>augusto_la32@hotmail.com</t>
         </is>
@@ -897,7 +909,7 @@
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
@@ -911,8 +923,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Jonatan Ariel Gonzalez</t>
         </is>
@@ -922,7 +934,7 @@
           <t>35,035,210</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Jonidespertad18@gmail.com</t>
         </is>
@@ -932,7 +944,7 @@
           <t>3777531414</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -947,7 +959,7 @@
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Melina Isabel Barbona</t>
         </is>
@@ -957,7 +969,7 @@
           <t>36,445,555</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>jonidespertad18@gmail.com</t>
         </is>
@@ -967,7 +979,7 @@
           <t>3777691836</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
@@ -982,7 +994,7 @@
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Abigail Martinez</t>
         </is>
@@ -992,7 +1004,7 @@
           <t>49,666,988</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>martineznahirabigail@gmail.com</t>
         </is>
@@ -1002,7 +1014,7 @@
           <t>3794096406</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Gustavo Escobar</t>
         </is>
@@ -1029,7 +1041,7 @@
           <t>95,259,056</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
@@ -1039,7 +1051,7 @@
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Ximena Robledo</t>
         </is>
@@ -1066,7 +1078,7 @@
           <t>5,321,660</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
@@ -1076,7 +1088,7 @@
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1093,7 +1105,7 @@
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Lourdes Coronek</t>
         </is>
@@ -1103,7 +1115,7 @@
           <t>95,216,658</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
@@ -1113,7 +1125,7 @@
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1130,7 +1142,7 @@
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Chapo Noelia Adriana</t>
         </is>
@@ -1140,7 +1152,7 @@
           <t>29,881,151</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Noeliaadrianachapo@gmail.com</t>
         </is>
@@ -1150,7 +1162,7 @@
           <t>3718545378</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1167,7 +1179,7 @@
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Jorge Jose Baez</t>
         </is>
@@ -1177,11 +1189,11 @@
           <t>28,420,407</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n"/>
+      <c r="C19" s="18" t="n"/>
       <c r="D19" s="12" t="n">
         <v>3718546293</v>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1198,7 +1210,7 @@
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Emanuel Baukloh</t>
         </is>
@@ -1208,7 +1220,7 @@
           <t>41,177,151</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>emanuelbaukloh@gmail.com</t>
         </is>
@@ -1218,7 +1230,7 @@
           <t>3718458439</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
@@ -1235,7 +1247,7 @@
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Francini Gustavo Daniel</t>
         </is>
@@ -1245,7 +1257,7 @@
           <t>37,884,991</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>gusfrancini@gmail.com</t>
         </is>
@@ -1255,7 +1267,7 @@
           <t>3794526768</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1272,7 +1284,7 @@
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Sotelo Maria Laura</t>
         </is>
@@ -1282,7 +1294,7 @@
           <t>38,876,535</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>sotelolaura209@gmail.com</t>
         </is>
@@ -1292,7 +1304,7 @@
           <t>3794235747</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Abril Steinle</t>
         </is>
@@ -1317,7 +1329,7 @@
       <c r="B23" s="7" t="n">
         <v>43066068</v>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>Steinleabril13@gmail.com</t>
         </is>
@@ -1327,7 +1339,7 @@
           <t>3794005300</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Maria Daniela Del Buono</t>
         </is>
@@ -1354,7 +1366,7 @@
           <t>31,849,062</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
@@ -1364,7 +1376,7 @@
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1379,7 +1391,7 @@
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Agustina Daniela Mantaras</t>
         </is>
@@ -1389,7 +1401,7 @@
           <t>46,785,165</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>agustinamantaras8@gmail.com</t>
         </is>
@@ -1399,7 +1411,7 @@
           <t>3764740347</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1414,7 +1426,7 @@
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Hector Luis Ayala</t>
         </is>
@@ -1424,7 +1436,7 @@
           <t>21,855,255</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
@@ -1434,7 +1446,7 @@
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1447,7 +1459,7 @@
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Irma Vallejos</t>
         </is>
@@ -1457,7 +1469,7 @@
           <t>14,663,815</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
@@ -1467,7 +1479,7 @@
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1480,7 +1492,7 @@
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Virginia Riveros</t>
         </is>
@@ -1490,7 +1502,7 @@
           <t>29,223,709</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
@@ -1500,7 +1512,7 @@
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
@@ -1513,7 +1525,7 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Florencia Cabral</t>
         </is>
@@ -1523,7 +1535,7 @@
           <t>51,520,144</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
@@ -1533,7 +1545,7 @@
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
@@ -1546,7 +1558,7 @@
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Debora Raquel Amarilla González</t>
         </is>
@@ -1556,7 +1568,7 @@
           <t>43,532,913</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>deboradrag15@gmail.com</t>
         </is>
@@ -1566,7 +1578,7 @@
           <t>3794023063</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>Voz que Clama</t>
         </is>
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Cabral Fernando R. Adrian</t>
         </is>
@@ -1589,17 +1601,17 @@
           <t>28,397,653</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>frac007@hotmail.com</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>54 9 362 4557191</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>Pacto de restauracion</t>
         </is>
@@ -1612,7 +1624,7 @@
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Victoria Valentina Ayala</t>
         </is>
@@ -1622,7 +1634,7 @@
           <t>46,718,239</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
@@ -1632,7 +1644,7 @@
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1645,7 +1657,7 @@
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Yeniffer Silvera Suárez</t>
         </is>
@@ -1655,7 +1667,7 @@
           <t>53,483,881</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>yensilsuar13@gmail.com</t>
         </is>
@@ -1665,7 +1677,7 @@
           <t>+598 094 135 946</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1678,7 +1690,7 @@
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>Renzo Acosta</t>
         </is>
@@ -1688,7 +1700,7 @@
           <t>54,848,640</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>acostarenzo975@gmail.com</t>
         </is>
@@ -1698,7 +1710,7 @@
           <t>+598 94 930 080</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1711,7 +1723,7 @@
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Gabriela Coronel</t>
         </is>
@@ -1721,7 +1733,7 @@
           <t>53,589,489</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>Sandracoronel.07@gmail.com</t>
         </is>
@@ -1731,7 +1743,7 @@
           <t>+598 93 640 559</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Nahuel Acosta</t>
         </is>
@@ -1754,7 +1766,7 @@
           <t>54,015,825</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>Nahuel_acosta12@hotmail.com</t>
         </is>
@@ -1764,7 +1776,7 @@
           <t>+598 94 805 438</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
@@ -1777,7 +1789,7 @@
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Noemí Roldán</t>
         </is>
@@ -1787,7 +1799,7 @@
           <t>56,349,232</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>noeroldan545@gmail.com</t>
         </is>
@@ -1797,7 +1809,7 @@
           <t>+598 092237179</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1810,7 +1822,7 @@
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Marcelo Andres Pirez Aquino</t>
         </is>
@@ -1820,7 +1832,7 @@
           <t>48,841,472</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>marcelopirez459@gmail.com</t>
         </is>
@@ -1830,7 +1842,7 @@
           <t>+598 096401066</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
@@ -1843,7 +1855,7 @@
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>Rosa Vallejos</t>
         </is>
@@ -1853,7 +1865,7 @@
           <t>12,687,300</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>Rosavallejos1805@gamail.com</t>
         </is>
@@ -1863,7 +1875,7 @@
           <t>3624-283862</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>Pacto de restauración central</t>
         </is>
@@ -1876,7 +1888,7 @@
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Yohana Belen Galarza</t>
         </is>
@@ -1886,7 +1898,7 @@
           <t>40,281,097</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>hous1516@gmail.com</t>
         </is>
@@ -1896,7 +1908,7 @@
           <t>3756596984</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="18" t="inlineStr">
         <is>
           <t>Centro Cristiano para las Familias</t>
         </is>
@@ -1909,7 +1921,7 @@
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>Gisela Davalos</t>
         </is>
@@ -1919,7 +1931,7 @@
           <t>36,317,286</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>gise130513@gmail.com</t>
         </is>
@@ -1929,7 +1941,7 @@
           <t>+54 9 3794 80-7731</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
@@ -1941,220 +1953,657 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="42" ht="18.75" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Matías Benjamín Velázquez Acuña</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>47,539,002</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>benjavel06@gmail.com</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>3794280284</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr">
         <is>
           <t>Iglesia Bautista del Amor</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18.75" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>Romina Noelia Acuña</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>32,880,155</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>ronoeliaacuna@gmail.com</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>3795033741</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="18" t="inlineStr">
         <is>
           <t>Iglesia Bautista del Amor</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18.75" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Nadia Montenegro</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>32,061,700</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>nadiaemilia5@gmail.com</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>3468-411458</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="18" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18.75" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Candela Basualdo Freytes</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>46,770,578</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>candebasfrey@gmail.com</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>3468642321</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="18" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18.75" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Arnold Tomas Pavon</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>44,296,431</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>candebasfrey@gmail.com</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>3468642321</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18.75" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Gustavo Scholles</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>gustavo123scholles@gmail.com</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>+54 9 3754 41-6387</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18.75" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Yolanda Alicia Reyes</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>20,312,303</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>Reyesyolanda5798@gmail.com</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>3794-976944</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="18" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18.75" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Misael Alejandro Pepa Grandi</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>48,683,524</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>misaelpepagrandi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>3644272071</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18.75" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>Viviana Amanda Mamani</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>18,040,124</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Vivianahaansen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>3873564045</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18.75" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>Priscila Elizabeth Mamani</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>45,365,213</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Vivianahaansen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>3873564045</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18.75" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>Marina de los Angeles Mamani</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>48,210,573</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Vivianahaansen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>3873564045</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18.75" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>Sergio Adolfo Basto</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>26,463,633</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Vivianahaansen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>3873564045</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18.75" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>Josias Vera</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>38,872,948</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>josiasvera14.jv@gmail.com</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>3704235704</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>Más que Vencedores Formosa</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18.75" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>Evangelina Caballero</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>36,204,752</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>josiasvera14.jv@gmail.com</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>3704235704</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>Más que Vencedores Formosa</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18.75" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>Ana María Gómez</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>14,202,308</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>analia04_82@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>3624790482</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>P.D.R.C.</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18.75" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>Vanesa Edith Escobar</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>28,047,269</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>analia04_82@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>3624790482</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>P.D.R.C.</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18.75" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>Ismael Vicente Villo</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>42,985,545</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>ismaelvillo18@gmail.com</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>3625635985</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18.75" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>Alfredo Portillo</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>14,236,041</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>Alfredocarlosportillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>3794595320</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iglesia Todo Es Posible </t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18.75" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>Silvia Sosa</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>16,478,463</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Alfredocarlosportillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>3794593220</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>Iglesia Todo Es Posible</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18.75" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>Florencia Daiana Acosta</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>39,564,040</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>acostaflorencia030@gmail.com</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>3795-157482</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="22" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>

--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25.005" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
@@ -2609,6 +2609,230 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Alexis Fabián Ledesma</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>48,343,561</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>alexisledesma446@gmail.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3782-514782</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lucila Abigail González Vedoya</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>48,343,546</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>iphoneevaristo49@gmail.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3782-611587</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Augusto Pedro Salvador González Vedoya</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>42,738,727</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>augustogonzalezvedoya254@gmail.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3782-443657</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Mateo Joaquín Barrientos</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>49,276,503</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>barrientomateo74@gmail.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3782-504340</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Yesica Mariela Vergara</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>39,633,517</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>vergarayesica045@gmail.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3782-418022</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gustavo Miguel Sánchez</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>37,430,616</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>vergarayesica045@gmail.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3782-418022</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mariel Abigail Barrientos</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>37,430,165</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>marielabby_921@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3782-519824</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Iglesia Shekina Saladas</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asistentes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,7 +27,7 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -53,7 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1e5aa0"/>
+        <fgColor rgb="FF1E5AA0"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,16 +67,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -101,9 +101,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -132,32 +129,12 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -240,10 +217,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -281,71 +258,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -373,7 +350,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -396,11 +373,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -409,13 +386,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -425,7 +402,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -434,7 +411,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -443,7 +420,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -451,10 +428,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -524,19 +501,19 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G104"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="25.005" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="19" min="2" max="2"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="18" min="3" max="3"/>
-    <col width="25.005" bestFit="1" customWidth="1" style="20" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="18" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="21" min="6" max="6"/>
-    <col width="15.005" bestFit="1" customWidth="1" style="22" min="7" max="7"/>
+    <col width="25" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="25" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="25" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="25" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
+    <col width="13.54296875" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
+    <col width="13.54296875" bestFit="1" customWidth="1" style="16" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
+    <row r="1" ht="19.5" customHeight="1" s="13">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>nombre_completo</t>
@@ -557,2053 +534,2031 @@
           <t>celular</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>congregacion</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1" s="13">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Marcia Lucrecia Lourdes Benitez</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>35,450,627</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>marciabenitezll@gmail.com</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>3794534177</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.5" customHeight="1" s="13">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Maira Melanie Ailen Benitez</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>42,097,841</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>ailenmelbenitez99@gmail.com</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>3795366654</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19.5" customHeight="1" s="13">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Analia Cambiaso</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>11,464,195</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1" s="13">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Anderson da Rocha Fernandes</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>95,276,764</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1" s="13">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Juliana Cristina Siqueira Fernandes</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>95,276,773</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>3777238654</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" s="13">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Samuel Siqueira Fernandes</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>95,279,778</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1" s="13">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Alan Lionel Gonzalez</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>48,399,343</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>3777222734</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19.5" customHeight="1" s="13">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Valentina Fernandes Siqueira</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>54,649,578</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1" s="13">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Vera Valeria Andrea</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>37,394,518</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>valeria_694202@hotmail.com</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" s="13">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Silvero Augusto Andres</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>36,674,838</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>augusto_la32@hotmail.com</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" s="13">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Jonatan Ariel Gonzalez</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>35,035,210</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Jonidespertad18@gmail.com</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>3777531414</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" s="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Melina Isabel Barbona</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>36,445,555</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>jonidespertad18@gmail.com</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>3777691836</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="13">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Abigail Martinez</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>49,666,988</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>martineznahirabigail@gmail.com</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>3794096406</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" s="13">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Gustavo Escobar</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>95,259,056</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" s="13">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Ximena Robledo</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>5,321,660</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" s="13">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Lourdes Coronek</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>95,216,658</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" s="13">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Chapo Noelia Adriana</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>29,881,151</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Noeliaadrianachapo@gmail.com</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>3718545378</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" s="13">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Jorge Jose Baez</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>28,420,407</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="11" t="n">
         <v>3718546293</v>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1" s="13">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Emanuel Baukloh</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>41,177,151</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>emanuelbaukloh@gmail.com</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>3718458439</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1" s="13">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Francini Gustavo Daniel</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>37,884,991</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>gusfrancini@gmail.com</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>3794526768</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1" s="13">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Sotelo Maria Laura</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>38,876,535</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>sotelolaura209@gmail.com</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>3794235747</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1" s="13">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Abril Steinle</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="6" t="n">
         <v>43066068</v>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Steinleabril13@gmail.com</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>3794005300</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>23/7/2026</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1" s="13">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Maria Daniela Del Buono</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>31,849,062</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="4" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1" s="13">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Agustina Daniela Mantaras</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>46,785,165</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>agustinamantaras8@gmail.com</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>3764740347</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="4" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" s="13">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Hector Luis Ayala</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>21,855,255</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1" s="13">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Irma Vallejos</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>14,663,815</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1" s="13">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Virginia Riveros</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>29,223,709</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1" s="13">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Florencia Cabral</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>51,520,144</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1" s="13">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Debora Raquel Amarilla González</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>43,532,913</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>deboradrag15@gmail.com</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>3794023063</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Voz que Clama</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1" s="13">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Cabral Fernando R. Adrian</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>28,397,653</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>frac007@hotmail.com</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>54 9 362 4557191</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Pacto de restauracion</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19.5" customHeight="1" s="13">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Victoria Valentina Ayala</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>46,718,239</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19.5" customHeight="1" s="13">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Yeniffer Silvera Suárez</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>53,483,881</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>yensilsuar13@gmail.com</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>+598 094 135 946</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1" s="13">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Renzo Acosta</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>54,848,640</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>acostarenzo975@gmail.com</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>+598 94 930 080</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1" s="13">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Gabriela Coronel</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>53,589,489</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Sandracoronel.07@gmail.com</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>+598 93 640 559</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1" s="13">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Nahuel Acosta</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>54,015,825</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Nahuel_acosta12@hotmail.com</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>+598 94 805 438</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1" s="13">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Noemí Roldán</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>56,349,232</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>noeroldan545@gmail.com</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>+598 092237179</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19.5" customHeight="1" s="13">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Marcelo Andres Pirez Aquino</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>48,841,472</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>marcelopirez459@gmail.com</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>+598 096401066</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19.5" customHeight="1" s="13">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Rosa Vallejos</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>12,687,300</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Rosavallejos1805@gamail.com</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>3624-283862</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Pacto de restauración central</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19.5" customHeight="1" s="13">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Yohana Belen Galarza</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>40,281,097</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>hous1516@gmail.com</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>3756596984</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Centro Cristiano para las Familias</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19.5" customHeight="1" s="13">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Gisela Davalos</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>36,317,286</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>gise130513@gmail.com</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>+54 9 3794 80-7731</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18.75" customHeight="1" s="13">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Matías Benjamín Velázquez Acuña</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>47,539,002</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>benjavel06@gmail.com</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>3794280284</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Iglesia Bautista del Amor</t>
         </is>
       </c>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18.75" customHeight="1" s="13">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Romina Noelia Acuña</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>32,880,155</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>ronoeliaacuna@gmail.com</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>3795033741</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Iglesia Bautista del Amor</t>
         </is>
       </c>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18.75" customHeight="1" s="13">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Nadia Montenegro</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>32,061,700</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>nadiaemilia5@gmail.com</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>3468-411458</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18.75" customHeight="1" s="13">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Candela Basualdo Freytes</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>46,770,578</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>candebasfrey@gmail.com</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>3468642321</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18.75" customHeight="1" s="13">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Arnold Tomas Pavon</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>44,296,431</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>candebasfrey@gmail.com</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>3468642321</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18.75" customHeight="1" s="13">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Gustavo Scholles</t>
         </is>
       </c>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>gustavo123scholles@gmail.com</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>+54 9 3754 41-6387</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18.75" customHeight="1" s="13">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Yolanda Alicia Reyes</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>20,312,303</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Reyesyolanda5798@gmail.com</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>3794-976944</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18.75" customHeight="1" s="13">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Misael Alejandro Pepa Grandi</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>48,683,524</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>misaelpepagrandi@gmail.com</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>3644272071</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
         </is>
       </c>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18.75" customHeight="1" s="13">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Viviana Amanda Mamani</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>18,040,124</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18.75" customHeight="1" s="13">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Priscila Elizabeth Mamani</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>45,365,213</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18.75" customHeight="1" s="13">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Marina de los Angeles Mamani</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>48,210,573</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18.75" customHeight="1" s="13">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Sergio Adolfo Basto</t>
         </is>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>26,463,633</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18.75" customHeight="1" s="13">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Josias Vera</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>38,872,948</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>josiasvera14.jv@gmail.com</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>3704235704</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Más que Vencedores Formosa</t>
         </is>
       </c>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18.75" customHeight="1" s="13">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Evangelina Caballero</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>36,204,752</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>josiasvera14.jv@gmail.com</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>3704235704</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Más que Vencedores Formosa</t>
         </is>
       </c>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18.75" customHeight="1" s="13">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Ana María Gómez</t>
         </is>
       </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>14,202,308</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>analia04_82@hotmail.com</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>3624790482</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>P.D.R.C.</t>
         </is>
       </c>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18.75" customHeight="1" s="13">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Vanesa Edith Escobar</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>28,047,269</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>analia04_82@hotmail.com</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>3624790482</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>P.D.R.C.</t>
         </is>
       </c>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18.75" customHeight="1" s="13">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Ismael Vicente Villo</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>42,985,545</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>ismaelvillo18@gmail.com</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>3625635985</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F58" s="21" t="n"/>
-      <c r="G58" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18.75" customHeight="1" s="13">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Alfredo Portillo</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>14,236,041</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Alfredocarlosportillo@gmail.com</t>
         </is>
       </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>3794595320</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">Iglesia Todo Es Posible </t>
         </is>
       </c>
-      <c r="F59" s="21" t="n"/>
-      <c r="G59" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18.75" customHeight="1" s="13">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Silvia Sosa</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>16,478,463</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Alfredocarlosportillo@gmail.com</t>
         </is>
       </c>
-      <c r="D60" s="20" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>3794593220</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Iglesia Todo Es Posible</t>
         </is>
       </c>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="22" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18.75" customHeight="1" s="13">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Florencia Daiana Acosta</t>
         </is>
       </c>
-      <c r="B61" s="19" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>39,564,040</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>acostaflorencia030@gmail.com</t>
         </is>
       </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>3795-157482</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F61" s="21" t="n"/>
-      <c r="G61" s="22" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>
@@ -2828,6 +2783,1158 @@
         </is>
       </c>
       <c r="G68" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ornella Tatiana Rodríguez Matiauda</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>37,585,027</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>orne5.05@gmail.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>+54 9 3794 04-0299</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Axel Fabián Diaz Gomez</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>47,227,898</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>daxel6213@gmail.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3731558685</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ivana Vazquez</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>28,336,634</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Vazquezivanarocio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3873303322</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jorge A. Fuensalida</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21,743,170</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>lalofuenzalida07@gmail.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3872540111</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hector Guillermo Bijou</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>36,193,969</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kiqui_hgb@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3482-663334</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Iglesia Tu Lugar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Malena Holenich</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>38,314,681</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kiqui_hgb@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3795-006209</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Iglesia Tu Lugar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Miguel Angel Nuñez</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>31,720,119</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>miguelangel31722@gmail.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3774-403544</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Iglesia Gran Rey Curuzú Cuatiá</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Angel Emmanuel Vallejos</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>34,341,510</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>abbyoliviavallejos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3781-498090</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Iglesia Gran Rey Curuzú Cuatiá</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Matías Jesús Romero</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>41,788,751</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Matiasjesusromero9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3774-444425</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Iglesia Gran Rey Curuzú Cuatiá</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Leonardo García</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>40,743,245</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>leo_eze.8@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3774-408370</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Iglesia Gran Rey Curuzú Cuatiá</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fernando Mathias Solonezki</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>33,487,622</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>msolonezki@gmail.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3755648165</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>La Congre Iglesia (Posadas Misiones)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Xiomara Tania Asís Wasylov</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>32,228,126</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>xiotaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3764715756</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>La Congre Iglesia (Posadas Misiones)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Juana Elena Wasylov</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>11,830,067</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>juanaelenaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3764316298</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>La Congre Iglesia (Posadas Misiones)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dionisio Agustín Asis</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>11,941,095</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>asisdionisio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>37643471</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>La Congre Iglesia (Posadas Misiones)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Yazmin Damaris Aquino</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>51,522,118</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Actas1983@gmail.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3624060544</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Iglesia Betania, Barranqueras, Chaco</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Juan Francisco Colman</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>30,705,778</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jfcolman@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3624222337</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Portal del Cielo - Resistencia, Chaco</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gabriel Ricardo León</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>38,565,094</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>gabrielleon.locutor@gmail.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3764874538</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Iglesia de Dios Posadas</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Nélida Gabriela Benitez</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>38,565,094</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>gabibenitez07@gmail.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3764761013</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Iglesia de Dios Posadas</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sebastián Avalos</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>28,397,564</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sebasg1080@gmail.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3624683615</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Pacto de Restauración, Barranqueras - Chaco</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Lisandro Canteros</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>47,336,963</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>lisandro12.canteros@gmail.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3487694156</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Directo al Corazón, Campana</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Thiago Andrade</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>45,805,348</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>iamthiagoandrade@gmail.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>11 5863-2265</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ministerio Nuevo Rumbo (Zárate, Buenos Aires)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>María Angelina Labrousse</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>29,721,560</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>angelinalab@gmail.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3794407003</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Iglesia Catedral del Espíritu Santo</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Romina Torres 1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>33,126,430</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>rominadespogrupo@outlook.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3772-441678</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Andrés Pepa</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>38,121,255</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>carlosandrespepa58@gmail.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3644-306017</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Selenne Stefanía Humar Cipriani</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>44,387,572</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>selenne-humar@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3731-623134</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Marilen Edith Moors</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>42,190,851</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>moorsmarilen072@gmail.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3624687250</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Iglesia Pacto de Restauración</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Romina Torres 2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>33,126,430</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>rominadespogrupo@outlook.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3772-441678</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Romina Torres 3</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>33,126,430</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>rominadespogrupo@outlook.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3772-441678</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Romina Torres 4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>33,126,430</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>rominadespogrupo@outlook.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3772-441678</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Romina Torres 5</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>33,126,430</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>rominadespogrupo@outlook.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3772-441678</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Luis Alfredo Chávez</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>18,433,887</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Alfredo549801@gmail.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3873549801</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Nelida Albina Villalba</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>20,544,350</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Alfredo549801@gmail.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3873549801</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Iglesia Somos Familia</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Scheila Alvez</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>43,068,555</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Scheilaalvez123@gmail.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3755220982</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Nicolás Fernando Eijo</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>40,582,751</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Nicoeijo97@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3624618352</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Portal del Cielo - Resistencia, Chaco</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ana Paula Lacour</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>46,076,265</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>lacouranapaula56@gmail.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3795-077377</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ricardo De Jesús Paredes</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>43,109,940</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>paredesric777@gmail.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3794-263339</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>

--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asistentes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,7 +27,7 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFffffff"/>
       <sz val="11"/>
     </font>
     <font>
@@ -43,6 +43,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -53,7 +59,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E5AA0"/>
+        <fgColor rgb="FF1e5aa0"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,16 +73,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </left>
       <right style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -91,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -101,6 +107,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -129,12 +138,47 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -217,10 +261,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -258,71 +302,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,7 +394,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -373,11 +417,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -386,13 +430,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -402,7 +446,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -411,7 +455,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -420,7 +464,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -428,10 +472,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -501,19 +545,19 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:G204"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="25" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="25" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
-    <col width="25" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
-    <col width="25" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
-    <col width="13.54296875" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
-    <col width="13.54296875" bestFit="1" customWidth="1" style="16" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" style="17" min="7" max="7"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="25.005" bestFit="1" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="26" min="6" max="6"/>
+    <col width="15.005" bestFit="1" customWidth="1" style="27" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="13">
+    <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>nombre_completo</t>
@@ -534,3407 +578,6632 @@
           <t>celular</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>congregacion</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1" s="13">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Marcia Lucrecia Lourdes Benitez</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>35,450,627</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>marciabenitezll@gmail.com</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>3794534177</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" s="13">
-      <c r="A3" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Maira Melanie Ailen Benitez</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>42,097,841</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>ailenmelbenitez99@gmail.com</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>3795366654</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1" s="13">
-      <c r="A4" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Analia Cambiaso</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>11,464,195</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="19.5" customHeight="1" s="13">
-      <c r="A5" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Anderson da Rocha Fernandes</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>95,276,764</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="19.5" customHeight="1" s="13">
-      <c r="A6" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Juliana Cristina Siqueira Fernandes</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>95,276,773</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>3777238654</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1" s="13">
-      <c r="A7" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Samuel Siqueira Fernandes</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>95,279,778</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="19.5" customHeight="1" s="13">
-      <c r="A8" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Alan Lionel Gonzalez</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>48,399,343</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>3777222734</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19.5" customHeight="1" s="13">
-      <c r="A9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Valentina Fernandes Siqueira</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>54,649,578</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>andersonfernandes000@gmail.com</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>3777307640</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19.5" customHeight="1" s="13">
-      <c r="A10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Vera Valeria Andrea</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>37,394,518</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>valeria_694202@hotmail.com</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19.5" customHeight="1" s="13">
-      <c r="A11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Silvero Augusto Andres</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>36,674,838</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>augusto_la32@hotmail.com</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>3795199587</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Congregacional Dios es Vida</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19.5" customHeight="1" s="13">
-      <c r="A12" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Jonatan Ariel Gonzalez</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>35,035,210</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Jonidespertad18@gmail.com</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>3777531414</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1" s="13">
-      <c r="A13" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Melina Isabel Barbona</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>36,445,555</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>jonidespertad18@gmail.com</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>3777691836</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> Iglesia Vida Nueva-Bella Vista Ctes</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1" s="13">
-      <c r="A14" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Abigail Martinez</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>49,666,988</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>martineznahirabigail@gmail.com</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>3794096406</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1" s="13">
-      <c r="A15" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Gustavo Escobar</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>95,259,056</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1" s="13">
-      <c r="A16" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Ximena Robledo</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>5,321,660</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1" s="13">
-      <c r="A17" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Lourdes Coronek</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>95,216,658</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>gescobarmqv@gmail.com</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>3718663215</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1" s="13">
-      <c r="A18" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Chapo Noelia Adriana</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>29,881,151</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Noeliaadrianachapo@gmail.com</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>3718545378</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1" s="13">
-      <c r="A19" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Jorge Jose Baez</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>28,420,407</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="12" t="n">
         <v>3718546293</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19.5" customHeight="1" s="13">
-      <c r="A20" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Emanuel Baukloh</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>41,177,151</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>emanuelbaukloh@gmail.com</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>3718458439</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Iglesia MQV</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1" s="13">
-      <c r="A21" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Francini Gustavo Daniel</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>37,884,991</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>gusfrancini@gmail.com</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>3794526768</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1" s="13">
-      <c r="A22" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Sotelo Maria Laura</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>38,876,535</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>sotelolaura209@gmail.com</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>3794235747</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>20/7/2026</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1" s="13">
-      <c r="A23" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Abril Steinle</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="7" t="n">
         <v>43066068</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Steinleabril13@gmail.com</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>3794005300</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>23/7/2026</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1" s="13">
-      <c r="A24" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Maria Daniela Del Buono</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>31,849,062</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>cambiasoanaliaitati130454@gmail.com</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>3794404946</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1" s="13">
-      <c r="A25" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Agustina Daniela Mantaras</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>46,785,165</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>agustinamantaras8@gmail.com</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>3764740347</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>25568.87529592593</v>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" s="13">
-      <c r="A26" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Hector Luis Ayala</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>21,855,255</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1" s="13">
-      <c r="A27" t="inlineStr">
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Irma Vallejos</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>14,663,815</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1" s="13">
-      <c r="A28" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Virginia Riveros</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>29,223,709</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1" s="13">
-      <c r="A29" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Florencia Cabral</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>51,520,144</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>florisabela54@gmail.com</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>3624-557157</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Pacto de Restauración</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1" s="13">
-      <c r="A30" t="inlineStr">
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>Debora Raquel Amarilla González</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>43,532,913</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>deboradrag15@gmail.com</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>3794023063</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Voz que Clama</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1" s="13">
-      <c r="A31" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Cabral Fernando R. Adrian</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>28,397,653</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>frac007@hotmail.com</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>54 9 362 4557191</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>Pacto de restauracion</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1" s="13">
-      <c r="A32" t="inlineStr">
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Victoria Valentina Ayala</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>46,718,239</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>hectorenfer@gmail.com</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>03795130209</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="19.5" customHeight="1" s="13">
-      <c r="A33" t="inlineStr">
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Yeniffer Silvera Suárez</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>53,483,881</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>yensilsuar13@gmail.com</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>+598 094 135 946</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="19.5" customHeight="1" s="13">
-      <c r="A34" t="inlineStr">
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Renzo Acosta</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>54,848,640</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>acostarenzo975@gmail.com</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>+598 94 930 080</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="19.5" customHeight="1" s="13">
-      <c r="A35" t="inlineStr">
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>Gabriela Coronel</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>53,589,489</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>Sandracoronel.07@gmail.com</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>+598 93 640 559</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19.5" customHeight="1" s="13">
-      <c r="A36" t="inlineStr">
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Nahuel Acosta</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>54,015,825</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>Nahuel_acosta12@hotmail.com</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>+598 94 805 438</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>Cristo en la Ciudad</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="19.5" customHeight="1" s="13">
-      <c r="A37" t="inlineStr">
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Noemí Roldán</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>56,349,232</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>noeroldan545@gmail.com</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>+598 092237179</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19.5" customHeight="1" s="13">
-      <c r="A38" t="inlineStr">
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>Marcelo Andres Pirez Aquino</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>48,841,472</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>marcelopirez459@gmail.com</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>+598 096401066</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>Cristo en la ciudad</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="19.5" customHeight="1" s="13">
-      <c r="A39" t="inlineStr">
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>Rosa Vallejos</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>12,687,300</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>Rosavallejos1805@gamail.com</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>3624-283862</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>Pacto de restauración central</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="19.5" customHeight="1" s="13">
-      <c r="A40" t="inlineStr">
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Yohana Belen Galarza</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>40,281,097</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>hous1516@gmail.com</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>3756596984</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>Centro Cristiano para las Familias</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19.5" customHeight="1" s="13">
-      <c r="A41" t="inlineStr">
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Gisela Davalos</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>36,317,286</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>gise130513@gmail.com</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>+54 9 3794 80-7731</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18.75" customHeight="1" s="13">
-      <c r="A42" t="inlineStr">
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18.75" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Matías Benjamín Velázquez Acuña</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>47,539,002</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>benjavel06@gmail.com</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>3794280284</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>Iglesia Bautista del Amor</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18.75" customHeight="1" s="13">
-      <c r="A43" t="inlineStr">
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18.75" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>Romina Noelia Acuña</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>32,880,155</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>ronoeliaacuna@gmail.com</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>3795033741</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>Iglesia Bautista del Amor</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18.75" customHeight="1" s="13">
-      <c r="A44" t="inlineStr">
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18.75" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>Nadia Montenegro</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>32,061,700</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>nadiaemilia5@gmail.com</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>3468-411458</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18.75" customHeight="1" s="13">
-      <c r="A45" t="inlineStr">
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18.75" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>Candela Basualdo Freytes</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>46,770,578</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>candebasfrey@gmail.com</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>3468642321</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18.75" customHeight="1" s="13">
-      <c r="A46" t="inlineStr">
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18.75" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>Arnold Tomas Pavon</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>44,296,431</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>candebasfrey@gmail.com</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>3468642321</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="23" t="inlineStr">
         <is>
           <t>Centro Cristiano Misiones Transmundiales Corral de Bustos</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18.75" customHeight="1" s="13">
-      <c r="A47" t="inlineStr">
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18.75" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>Gustavo Scholles</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>gustavo123scholles@gmail.com</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>+54 9 3754 41-6387</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18.75" customHeight="1" s="13">
-      <c r="A48" t="inlineStr">
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18.75" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>Yolanda Alicia Reyes</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>20,312,303</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>Reyesyolanda5798@gmail.com</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>3794-976944</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18.75" customHeight="1" s="13">
-      <c r="A49" t="inlineStr">
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18.75" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>Misael Alejandro Pepa Grandi</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>48,683,524</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>misaelpepagrandi@gmail.com</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>3644272071</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18.75" customHeight="1" s="13">
-      <c r="A50" t="inlineStr">
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18.75" customHeight="1">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>Viviana Amanda Mamani</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>18,040,124</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18.75" customHeight="1" s="13">
-      <c r="A51" t="inlineStr">
+      <c r="F50" s="14" t="n"/>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18.75" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>Priscila Elizabeth Mamani</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>45,365,213</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18.75" customHeight="1" s="13">
-      <c r="A52" t="inlineStr">
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18.75" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>Marina de los Angeles Mamani</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>48,210,573</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18.75" customHeight="1" s="13">
-      <c r="A53" t="inlineStr">
+      <c r="F52" s="14" t="n"/>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18.75" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>Sergio Adolfo Basto</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>26,463,633</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="23" t="inlineStr">
         <is>
           <t>Vivianahaansen@gmail.com</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>3873564045</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18.75" customHeight="1" s="13">
-      <c r="A54" t="inlineStr">
+      <c r="F53" s="14" t="n"/>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18.75" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t>Josias Vera</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>38,872,948</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>josiasvera14.jv@gmail.com</t>
         </is>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>3704235704</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>Más que Vencedores Formosa</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18.75" customHeight="1" s="13">
-      <c r="A55" t="inlineStr">
+      <c r="F54" s="14" t="n"/>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18.75" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>Evangelina Caballero</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>36,204,752</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>josiasvera14.jv@gmail.com</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>3704235704</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>Más que Vencedores Formosa</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18.75" customHeight="1" s="13">
-      <c r="A56" t="inlineStr">
+      <c r="F55" s="14" t="n"/>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18.75" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>Ana María Gómez</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>14,202,308</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
         <is>
           <t>analia04_82@hotmail.com</t>
         </is>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>3624790482</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>P.D.R.C.</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18.75" customHeight="1" s="13">
-      <c r="A57" t="inlineStr">
+      <c r="F56" s="14" t="n"/>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18.75" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>Vanesa Edith Escobar</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>28,047,269</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="23" t="inlineStr">
         <is>
           <t>analia04_82@hotmail.com</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>3624790482</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>P.D.R.C.</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18.75" customHeight="1" s="13">
-      <c r="A58" t="inlineStr">
+      <c r="F57" s="14" t="n"/>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18.75" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>Ismael Vicente Villo</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>42,985,545</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="23" t="inlineStr">
         <is>
           <t>ismaelvillo18@gmail.com</t>
         </is>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>3625635985</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18.75" customHeight="1" s="13">
-      <c r="A59" t="inlineStr">
+      <c r="F58" s="14" t="n"/>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18.75" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>Alfredo Portillo</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>14,236,041</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="23" t="inlineStr">
         <is>
           <t>Alfredocarlosportillo@gmail.com</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>3794595320</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Iglesia Todo Es Posible </t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18.75" customHeight="1" s="13">
-      <c r="A60" t="inlineStr">
+      <c r="F59" s="14" t="n"/>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18.75" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>Silvia Sosa</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>16,478,463</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="23" t="inlineStr">
         <is>
           <t>Alfredocarlosportillo@gmail.com</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>3794593220</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="23" t="inlineStr">
         <is>
           <t>Iglesia Todo Es Posible</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18.75" customHeight="1" s="13">
-      <c r="A61" t="inlineStr">
+      <c r="F60" s="14" t="n"/>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18.75" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t>Florencia Daiana Acosta</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>39,564,040</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="23" t="inlineStr">
         <is>
           <t>acostaflorencia030@gmail.com</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>3795-157482</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="F61" s="14" t="n"/>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18.75" customHeight="1">
+      <c r="A62" s="23" t="inlineStr">
         <is>
           <t>Alexis Fabián Ledesma</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>48,343,561</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
         <is>
           <t>alexisledesma446@gmail.com</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>3782-514782</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="F62" s="14" t="n"/>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18.75" customHeight="1">
+      <c r="A63" s="23" t="inlineStr">
         <is>
           <t>Lucila Abigail González Vedoya</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>48,343,546</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="23" t="inlineStr">
         <is>
           <t>iphoneevaristo49@gmail.com</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>3782-611587</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="F63" s="14" t="n"/>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18.75" customHeight="1">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>Augusto Pedro Salvador González Vedoya</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>42,738,727</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="23" t="inlineStr">
         <is>
           <t>augustogonzalezvedoya254@gmail.com</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>3782-443657</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="F64" s="14" t="n"/>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18.75" customHeight="1">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>Mateo Joaquín Barrientos</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>49,276,503</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>barrientomateo74@gmail.com</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>3782-504340</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="F65" s="14" t="n"/>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18.75" customHeight="1">
+      <c r="A66" s="23" t="inlineStr">
         <is>
           <t>Yesica Mariela Vergara</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>39,633,517</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="23" t="inlineStr">
         <is>
           <t>vergarayesica045@gmail.com</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>3782-418022</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="F66" s="14" t="n"/>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18.75" customHeight="1">
+      <c r="A67" s="23" t="inlineStr">
         <is>
           <t>Gustavo Miguel Sánchez</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>37,430,616</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
         <is>
           <t>vergarayesica045@gmail.com</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>3782-418022</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="F67" s="14" t="n"/>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18.75" customHeight="1">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>Mariel Abigail Barrientos</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>37,430,165</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
         <is>
           <t>marielabby_921@hotmail.com</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>3782-519824</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="23" t="inlineStr">
         <is>
           <t>Iglesia Shekina Saladas</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="F68" s="14" t="n"/>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18.75" customHeight="1">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>Ornella Tatiana Rodríguez Matiauda</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>37,585,027</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
         <is>
           <t>orne5.05@gmail.com</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>+54 9 3794 04-0299</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="F69" s="14" t="n"/>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18.75" customHeight="1">
+      <c r="A70" s="23" t="inlineStr">
         <is>
           <t>Axel Fabián Diaz Gomez</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>47,227,898</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>daxel6213@gmail.com</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>3731558685</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="F70" s="14" t="n"/>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18.75" customHeight="1">
+      <c r="A71" s="23" t="inlineStr">
         <is>
           <t>Ivana Vazquez</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>28,336,634</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="23" t="inlineStr">
         <is>
           <t>Vazquezivanarocio@gmail.com</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>3873303322</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="F71" s="14" t="n"/>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18.75" customHeight="1">
+      <c r="A72" s="23" t="inlineStr">
         <is>
           <t>Jorge A. Fuensalida</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>21,743,170</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="23" t="inlineStr">
         <is>
           <t>lalofuenzalida07@gmail.com</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>3872540111</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18.75" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
         <is>
           <t>Hector Guillermo Bijou</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>36,193,969</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
         <is>
           <t>kiqui_hgb@hotmail.com</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>3482-663334</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="23" t="inlineStr">
         <is>
           <t>Iglesia Tu Lugar</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18.75" customHeight="1">
+      <c r="A74" s="23" t="inlineStr">
         <is>
           <t>Malena Holenich</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>38,314,681</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="23" t="inlineStr">
         <is>
           <t>kiqui_hgb@hotmail.com</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>3795-006209</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="23" t="inlineStr">
         <is>
           <t>Iglesia Tu Lugar</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="F74" s="14" t="n"/>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18.75" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
         <is>
           <t>Miguel Angel Nuñez</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>31,720,119</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="23" t="inlineStr">
         <is>
           <t>miguelangel31722@gmail.com</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>3774-403544</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="23" t="inlineStr">
         <is>
           <t>Iglesia Gran Rey Curuzú Cuatiá</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="F75" s="14" t="n"/>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18.75" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>Angel Emmanuel Vallejos</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>34,341,510</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="23" t="inlineStr">
         <is>
           <t>abbyoliviavallejos@gmail.com</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>3781-498090</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="23" t="inlineStr">
         <is>
           <t>Iglesia Gran Rey Curuzú Cuatiá</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="F76" s="14" t="n"/>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18.75" customHeight="1">
+      <c r="A77" s="23" t="inlineStr">
         <is>
           <t>Matías Jesús Romero</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>41,788,751</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="23" t="inlineStr">
         <is>
           <t>Matiasjesusromero9@gmail.com</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>3774-444425</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="23" t="inlineStr">
         <is>
           <t>Iglesia Gran Rey Curuzú Cuatiá</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="F77" s="14" t="n"/>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18.75" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t>Leonardo García</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>40,743,245</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="23" t="inlineStr">
         <is>
           <t>leo_eze.8@hotmail.com</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>3774-408370</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="23" t="inlineStr">
         <is>
           <t>Iglesia Gran Rey Curuzú Cuatiá</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="F78" s="14" t="n"/>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18.75" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
         <is>
           <t>Fernando Mathias Solonezki</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>33,487,622</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="23" t="inlineStr">
         <is>
           <t>msolonezki@gmail.com</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>3755648165</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="23" t="inlineStr">
         <is>
           <t>La Congre Iglesia (Posadas Misiones)</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="F79" s="14" t="n"/>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18.75" customHeight="1">
+      <c r="A80" s="23" t="inlineStr">
         <is>
           <t>Xiomara Tania Asís Wasylov</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>32,228,126</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="23" t="inlineStr">
         <is>
           <t>xiotaw@gmail.com</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>3764715756</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="23" t="inlineStr">
         <is>
           <t>La Congre Iglesia (Posadas Misiones)</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="F80" s="14" t="n"/>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18.75" customHeight="1">
+      <c r="A81" s="23" t="inlineStr">
         <is>
           <t>Juana Elena Wasylov</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>11,830,067</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="23" t="inlineStr">
         <is>
           <t>juanaelenaw@gmail.com</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="17" t="inlineStr">
         <is>
           <t>3764316298</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="23" t="inlineStr">
         <is>
           <t>La Congre Iglesia (Posadas Misiones)</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="F81" s="14" t="n"/>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18.75" customHeight="1">
+      <c r="A82" s="23" t="inlineStr">
         <is>
           <t>Dionisio Agustín Asis</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>11,941,095</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="23" t="inlineStr">
         <is>
           <t>asisdionisio@gmail.com</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>37643471</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="23" t="inlineStr">
         <is>
           <t>La Congre Iglesia (Posadas Misiones)</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="F82" s="14" t="n"/>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18.75" customHeight="1">
+      <c r="A83" s="23" t="inlineStr">
         <is>
           <t>Yazmin Damaris Aquino</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>51,522,118</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="23" t="inlineStr">
         <is>
           <t>Actas1983@gmail.com</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>3624060544</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="23" t="inlineStr">
         <is>
           <t>Iglesia Betania, Barranqueras, Chaco</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="F83" s="14" t="n"/>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18.75" customHeight="1">
+      <c r="A84" s="23" t="inlineStr">
         <is>
           <t>Juan Francisco Colman</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>30,705,778</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="23" t="inlineStr">
         <is>
           <t>jfcolman@hotmail.com</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>3624222337</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="23" t="inlineStr">
         <is>
           <t>Portal del Cielo - Resistencia, Chaco</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="F84" s="14" t="n"/>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18.75" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>Gabriel Ricardo León</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>38,565,094</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="23" t="inlineStr">
         <is>
           <t>gabrielleon.locutor@gmail.com</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>3764874538</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="23" t="inlineStr">
         <is>
           <t>Iglesia de Dios Posadas</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="F85" s="14" t="n"/>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18.75" customHeight="1">
+      <c r="A86" s="23" t="inlineStr">
         <is>
           <t>Nélida Gabriela Benitez</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>38,565,094</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="23" t="inlineStr">
         <is>
           <t>gabibenitez07@gmail.com</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>3764761013</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="23" t="inlineStr">
         <is>
           <t>Iglesia de Dios Posadas</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="F86" s="14" t="n"/>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18.75" customHeight="1">
+      <c r="A87" s="23" t="inlineStr">
         <is>
           <t>Sebastián Avalos</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>28,397,564</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="23" t="inlineStr">
         <is>
           <t>sebasg1080@gmail.com</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>3624683615</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="23" t="inlineStr">
         <is>
           <t>Pacto de Restauración, Barranqueras - Chaco</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="F87" s="14" t="n"/>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18.75" customHeight="1">
+      <c r="A88" s="23" t="inlineStr">
         <is>
           <t>Lisandro Canteros</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>47,336,963</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="23" t="inlineStr">
         <is>
           <t>lisandro12.canteros@gmail.com</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>3487694156</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="23" t="inlineStr">
         <is>
           <t>Directo al Corazón, Campana</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="F88" s="14" t="n"/>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18.75" customHeight="1">
+      <c r="A89" s="23" t="inlineStr">
         <is>
           <t>Thiago Andrade</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>45,805,348</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="23" t="inlineStr">
         <is>
           <t>iamthiagoandrade@gmail.com</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>11 5863-2265</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="23" t="inlineStr">
         <is>
           <t>Ministerio Nuevo Rumbo (Zárate, Buenos Aires)</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="F89" s="14" t="n"/>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18.75" customHeight="1">
+      <c r="A90" s="23" t="inlineStr">
         <is>
           <t>María Angelina Labrousse</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t>29,721,560</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="23" t="inlineStr">
         <is>
           <t>angelinalab@gmail.com</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>3794407003</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="23" t="inlineStr">
         <is>
           <t>Iglesia Catedral del Espíritu Santo</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="F90" s="14" t="n"/>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18.75" customHeight="1">
+      <c r="A91" s="23" t="inlineStr">
         <is>
           <t>Romina Torres 1</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>33,126,430</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="23" t="inlineStr">
         <is>
           <t>rominadespogrupo@outlook.com</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>3772-441678</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="23" t="inlineStr">
         <is>
           <t>Sin congregación</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="F91" s="14" t="n"/>
+      <c r="G91" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18.75" customHeight="1">
+      <c r="A92" s="23" t="inlineStr">
         <is>
           <t>Andrés Pepa</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="16" t="inlineStr">
         <is>
           <t>38,121,255</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="23" t="inlineStr">
         <is>
           <t>carlosandrespepa58@gmail.com</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="17" t="inlineStr">
         <is>
           <t>3644-306017</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="23" t="inlineStr">
         <is>
           <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="F92" s="14" t="n"/>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18.75" customHeight="1">
+      <c r="A93" s="23" t="inlineStr">
         <is>
           <t>Selenne Stefanía Humar Cipriani</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>44,387,572</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="23" t="inlineStr">
         <is>
           <t>selenne-humar@hotmail.com</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="17" t="inlineStr">
         <is>
           <t>3731-623134</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="23" t="inlineStr">
         <is>
           <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="F93" s="14" t="n"/>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18.75" customHeight="1">
+      <c r="A94" s="23" t="inlineStr">
         <is>
           <t>Marilen Edith Moors</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>42,190,851</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="23" t="inlineStr">
         <is>
           <t>moorsmarilen072@gmail.com</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>3624687250</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="23" t="inlineStr">
         <is>
           <t>Iglesia Pacto de Restauración</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="F94" s="14" t="n"/>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18.75" customHeight="1">
+      <c r="A95" s="23" t="inlineStr">
         <is>
           <t>Romina Torres 2</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>33,126,430</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="23" t="inlineStr">
         <is>
           <t>rominadespogrupo@outlook.com</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="17" t="inlineStr">
         <is>
           <t>3772-441678</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="23" t="inlineStr">
         <is>
           <t>Sin congregación</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="F95" s="14" t="n"/>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18.75" customHeight="1">
+      <c r="A96" s="23" t="inlineStr">
         <is>
           <t>Romina Torres 3</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>33,126,430</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="23" t="inlineStr">
         <is>
           <t>rominadespogrupo@outlook.com</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="17" t="inlineStr">
         <is>
           <t>3772-441678</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="23" t="inlineStr">
         <is>
           <t>Sin congregación</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="F96" s="14" t="n"/>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18.75" customHeight="1">
+      <c r="A97" s="23" t="inlineStr">
         <is>
           <t>Romina Torres 4</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>33,126,430</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="23" t="inlineStr">
         <is>
           <t>rominadespogrupo@outlook.com</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="17" t="inlineStr">
         <is>
           <t>3772-441678</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="23" t="inlineStr">
         <is>
           <t>Sin congregación</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="F97" s="14" t="n"/>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18.75" customHeight="1">
+      <c r="A98" s="23" t="inlineStr">
         <is>
           <t>Romina Torres 5</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>33,126,430</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="23" t="inlineStr">
         <is>
           <t>rominadespogrupo@outlook.com</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="17" t="inlineStr">
         <is>
           <t>3772-441678</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="23" t="inlineStr">
         <is>
           <t>Sin congregación</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="F98" s="14" t="n"/>
+      <c r="G98" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18.75" customHeight="1">
+      <c r="A99" s="23" t="inlineStr">
         <is>
           <t>Luis Alfredo Chávez</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="16" t="inlineStr">
         <is>
           <t>18,433,887</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="23" t="inlineStr">
         <is>
           <t>Alfredo549801@gmail.com</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="17" t="inlineStr">
         <is>
           <t>3873549801</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="F99" s="14" t="n"/>
+      <c r="G99" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18.75" customHeight="1">
+      <c r="A100" s="23" t="inlineStr">
         <is>
           <t>Nelida Albina Villalba</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>20,544,350</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="23" t="inlineStr">
         <is>
           <t>Alfredo549801@gmail.com</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="17" t="inlineStr">
         <is>
           <t>3873549801</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="23" t="inlineStr">
         <is>
           <t>Iglesia Somos Familia</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="F100" s="14" t="n"/>
+      <c r="G100" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18.75" customHeight="1">
+      <c r="A101" s="23" t="inlineStr">
         <is>
           <t>Scheila Alvez</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="16" t="inlineStr">
         <is>
           <t>43,068,555</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="23" t="inlineStr">
         <is>
           <t>Scheilaalvez123@gmail.com</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="17" t="inlineStr">
         <is>
           <t>3755220982</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="F101" s="14" t="n"/>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18.75" customHeight="1">
+      <c r="A102" s="23" t="inlineStr">
         <is>
           <t>Nicolás Fernando Eijo</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="16" t="inlineStr">
         <is>
           <t>40,582,751</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="23" t="inlineStr">
         <is>
           <t>Nicoeijo97@hotmail.com</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="17" t="inlineStr">
         <is>
           <t>3624618352</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="23" t="inlineStr">
         <is>
           <t>Portal del Cielo - Resistencia, Chaco</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="F102" s="14" t="n"/>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18.75" customHeight="1">
+      <c r="A103" s="23" t="inlineStr">
         <is>
           <t>Ana Paula Lacour</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="16" t="inlineStr">
         <is>
           <t>46,076,265</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="23" t="inlineStr">
         <is>
           <t>lacouranapaula56@gmail.com</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="17" t="inlineStr">
         <is>
           <t>3795-077377</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="F103" s="14" t="n"/>
+      <c r="G103" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18.75" customHeight="1">
+      <c r="A104" s="23" t="inlineStr">
         <is>
           <t>Ricardo De Jesús Paredes</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>43,109,940</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="23" t="inlineStr">
         <is>
           <t>paredesric777@gmail.com</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="17" t="inlineStr">
         <is>
           <t>3794-263339</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="23" t="inlineStr">
         <is>
           <t>VQC</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="F104" s="14" t="n"/>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18.75" customHeight="1">
+      <c r="A105" s="23" t="inlineStr">
+        <is>
+          <t>Camila Antonella Galvan Lusa</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>40,608,183</t>
+        </is>
+      </c>
+      <c r="C105" s="23" t="inlineStr">
+        <is>
+          <t>camihanto@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>3644718788</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia de la Ciudad - Campo Largo Chaco</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="n"/>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18.75" customHeight="1">
+      <c r="A106" s="23" t="inlineStr">
+        <is>
+          <t>María de los Ángeles Reinante</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>24,620,852</t>
+        </is>
+      </c>
+      <c r="C106" s="23" t="inlineStr">
+        <is>
+          <t>marianreinante@gmail.com</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>3764835841</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="inlineStr">
+        <is>
+          <t>La Congre Iglesia (Posadas Misiones)</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="n"/>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18.75" customHeight="1">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>Cintia Karen Ortiz</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>41,306,065</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>cintiakarenortiz1998@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>3754-520145</t>
+        </is>
+      </c>
+      <c r="E107" s="23" t="inlineStr">
+        <is>
+          <t>La Congre</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="n"/>
+      <c r="G107" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18.75" customHeight="1">
+      <c r="A108" s="23" t="inlineStr">
+        <is>
+          <t>Fernando Blanch</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>36,929,607</t>
+        </is>
+      </c>
+      <c r="C108" s="23" t="inlineStr">
+        <is>
+          <t>fer_ab_05@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>3764721063</t>
+        </is>
+      </c>
+      <c r="E108" s="23" t="inlineStr">
+        <is>
+          <t>La Congre</t>
+        </is>
+      </c>
+      <c r="F108" s="14" t="n"/>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18.75" customHeight="1">
+      <c r="A109" s="23" t="inlineStr">
+        <is>
+          <t>Damaris Parra</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>48,195,179</t>
+        </is>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>damarissparra07@gmail.com</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>3704986130</t>
+        </is>
+      </c>
+      <c r="E109" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia de Dios</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="n"/>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18.75" customHeight="1">
+      <c r="A110" s="23" t="inlineStr">
+        <is>
+          <t>Valeria Noemi Padrón</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>30,589,964</t>
+        </is>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>valeriapadron1981@gmail.com</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>3704685730</t>
+        </is>
+      </c>
+      <c r="E110" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia de Dios</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="n"/>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18.75" customHeight="1">
+      <c r="A111" s="23" t="inlineStr">
+        <is>
+          <t>Karen Ailen Lachowski</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>45,045,985</t>
+        </is>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>Karenlachowski0@gmail.com</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>3735607416</t>
+        </is>
+      </c>
+      <c r="E111" s="23" t="inlineStr">
+        <is>
+          <t>Buenas Nuevas</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="n"/>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18.75" customHeight="1">
+      <c r="A112" s="23" t="inlineStr">
+        <is>
+          <t>Angel Fabian Alvarez</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>34,901,185</t>
+        </is>
+      </c>
+      <c r="C112" s="23" t="inlineStr">
+        <is>
+          <t>angelgenoves1212@gmail.com</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t>3644413455</t>
+        </is>
+      </c>
+      <c r="E112" s="23" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="n"/>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18.75" customHeight="1">
+      <c r="A113" s="23" t="inlineStr">
+        <is>
+          <t>Victor Gabriel Cañete</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>39,750,549</t>
+        </is>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>angelgenoves1212@gmail.com</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>3644413455</t>
+        </is>
+      </c>
+      <c r="E113" s="23" t="inlineStr">
+        <is>
+          <t>Sin congregación</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="n"/>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18.75" customHeight="1">
+      <c r="A114" s="23" t="inlineStr">
+        <is>
+          <t>Francesco Marano</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>3,351,983</t>
+        </is>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
+        <is>
+          <t>francescoasyaministries@gmail.com</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>+39 3207507464</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="inlineStr">
+        <is>
+          <t>Chiesa Gloriosa Roma</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="n"/>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18.75" customHeight="1">
+      <c r="A115" s="23" t="inlineStr">
+        <is>
+          <t>Asya De Salvatore</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>3,077,422</t>
+        </is>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>francescoasyaministries@gmail.com</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>+39 3884736405</t>
+        </is>
+      </c>
+      <c r="E115" s="23" t="inlineStr">
+        <is>
+          <t>Chiesa Gloriosa Roma</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="n"/>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18.75" customHeight="1">
+      <c r="A116" s="23" t="inlineStr">
+        <is>
+          <t>María Fernández</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>10,820,428</t>
+        </is>
+      </c>
+      <c r="C116" s="23" t="n"/>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>3794824978</t>
+        </is>
+      </c>
+      <c r="E116" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="n"/>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18.75" customHeight="1">
+      <c r="A117" s="23" t="inlineStr">
+        <is>
+          <t>Eleana Abigail Rodriguez</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>42,060,605</t>
+        </is>
+      </c>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>elerodriguez20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>3794272760</t>
+        </is>
+      </c>
+      <c r="E117" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia Elim</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="n"/>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18.75" customHeight="1">
+      <c r="A118" s="23" t="inlineStr">
+        <is>
+          <t>Hugo Amalio</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>42,378,502</t>
+        </is>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>huguitoamalio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>3624965370</t>
+        </is>
+      </c>
+      <c r="E118" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="n"/>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18.75" customHeight="1">
+      <c r="A119" s="23" t="inlineStr">
+        <is>
+          <t>Irma Itati Alvides</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>28,244,174</t>
+        </is>
+      </c>
+      <c r="C119" s="23" t="n"/>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>01160149467</t>
+        </is>
+      </c>
+      <c r="E119" s="23" t="inlineStr">
+        <is>
+          <t>Ministerio Evangelístico Bethel</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="n"/>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18.75" customHeight="1">
+      <c r="A120" s="23" t="inlineStr">
+        <is>
+          <t>Carlos Ramón Lizasoain</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>30,881,247</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="n"/>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>01166940376</t>
+        </is>
+      </c>
+      <c r="E120" s="23" t="inlineStr">
+        <is>
+          <t>Ministerio Evangelístico Bethel</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="n"/>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18.75" customHeight="1">
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t>Uziel Nehemías Lizasoain</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>52,415,593</t>
+        </is>
+      </c>
+      <c r="C121" s="23" t="n"/>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>01160149467</t>
+        </is>
+      </c>
+      <c r="E121" s="23" t="inlineStr">
+        <is>
+          <t>Ministerio Evangelístico Bethel</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="n"/>
+      <c r="G121" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18.75" customHeight="1">
+      <c r="A122" s="23" t="inlineStr">
+        <is>
+          <t>Uma Milagros Lizasoain</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>54,738,822</t>
+        </is>
+      </c>
+      <c r="C122" s="23" t="n"/>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>01166940376</t>
+        </is>
+      </c>
+      <c r="E122" s="23" t="inlineStr">
+        <is>
+          <t>Ministerio Evangelístico Bethel</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="n"/>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18.75" customHeight="1">
+      <c r="A123" s="23" t="inlineStr">
+        <is>
+          <t>Iara Janet Valdez</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>48,892,669</t>
+        </is>
+      </c>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>Valdez13iara@gmail.com</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>+54 9 362 415-7756</t>
+        </is>
+      </c>
+      <c r="E123" s="23" t="inlineStr">
+        <is>
+          <t>CCF Rhema - Resistencia, Chaco</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="n"/>
+      <c r="G123" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18.75" customHeight="1">
+      <c r="A124" s="23" t="inlineStr">
+        <is>
+          <t>Melina Portillo</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>41,607,930</t>
+        </is>
+      </c>
+      <c r="C124" s="23" t="inlineStr">
+        <is>
+          <t>Yoselieportillo07@gmail.com</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t>3704562222</t>
+        </is>
+      </c>
+      <c r="E124" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="n"/>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18.75" customHeight="1">
+      <c r="A125" s="23" t="inlineStr">
+        <is>
+          <t>Antonela Portillo</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>43,711,628</t>
+        </is>
+      </c>
+      <c r="C125" s="23" t="inlineStr">
+        <is>
+          <t>portilloantonelaayelen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>3725555860</t>
+        </is>
+      </c>
+      <c r="E125" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="n"/>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18.75" customHeight="1">
+      <c r="A126" s="23" t="inlineStr">
+        <is>
+          <t>Ricardo Peralta</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>44,652,193</t>
+        </is>
+      </c>
+      <c r="C126" s="23" t="inlineStr">
+        <is>
+          <t>rikiiperalta25@gmail.com</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>3794982284</t>
+        </is>
+      </c>
+      <c r="E126" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="n"/>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18.75" customHeight="1">
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>Facundo Sivisstum</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>4,424,926</t>
+        </is>
+      </c>
+      <c r="C127" s="23" t="inlineStr">
+        <is>
+          <t>facumdosuper@gmail.com</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>3795052749</t>
+        </is>
+      </c>
+      <c r="E127" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="n"/>
+      <c r="G127" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18.75" customHeight="1">
+      <c r="A128" s="23" t="inlineStr">
+        <is>
+          <t>Danielle Sivisstum</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>51,006,673</t>
+        </is>
+      </c>
+      <c r="C128" s="23" t="inlineStr">
+        <is>
+          <t>danisiviss@gmail.com</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>3794233524</t>
+        </is>
+      </c>
+      <c r="E128" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="n"/>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18.75" customHeight="1">
+      <c r="A129" s="23" t="inlineStr">
+        <is>
+          <t>Amira Nuñez</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>45,027,709</t>
+        </is>
+      </c>
+      <c r="C129" s="23" t="inlineStr">
+        <is>
+          <t>amiranaimnunez@gmail.com</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>3751231203</t>
+        </is>
+      </c>
+      <c r="E129" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="n"/>
+      <c r="G129" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18.75" customHeight="1">
+      <c r="A130" s="23" t="inlineStr">
+        <is>
+          <t>Débora Pómes</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>40,702,217</t>
+        </is>
+      </c>
+      <c r="C130" s="23" t="inlineStr">
+        <is>
+          <t>pomesdebora4@icloud.com</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>3794150958</t>
+        </is>
+      </c>
+      <c r="E130" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="n"/>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18.75" customHeight="1">
+      <c r="A131" s="23" t="inlineStr">
+        <is>
+          <t>Gianella Sue</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>45,707,221</t>
+        </is>
+      </c>
+      <c r="C131" s="23" t="inlineStr">
+        <is>
+          <t>Seugianella418@gmail.com</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>3794016157</t>
+        </is>
+      </c>
+      <c r="E131" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="n"/>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18.75" customHeight="1">
+      <c r="A132" s="23" t="inlineStr">
+        <is>
+          <t>Germán Lachowski</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>46,518,665</t>
+        </is>
+      </c>
+      <c r="C132" s="23" t="inlineStr">
+        <is>
+          <t>germanyt507@gmail.com</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>3735452064</t>
+        </is>
+      </c>
+      <c r="E132" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="n"/>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18.75" customHeight="1">
+      <c r="A133" s="23" t="inlineStr">
+        <is>
+          <t>Exequiel Ayala</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>37,393,261</t>
+        </is>
+      </c>
+      <c r="C133" s="23" t="inlineStr">
+        <is>
+          <t>ayalahectorexequiel@gmail.com</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="inlineStr">
+        <is>
+          <t>3794066581</t>
+        </is>
+      </c>
+      <c r="E133" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="n"/>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18.75" customHeight="1">
+      <c r="A134" s="23" t="inlineStr">
+        <is>
+          <t>Agustín Lotke</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>46,480,254</t>
+        </is>
+      </c>
+      <c r="C134" s="23" t="inlineStr">
+        <is>
+          <t>lotkeagustineloy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>3755537124</t>
+        </is>
+      </c>
+      <c r="E134" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="n"/>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18.75" customHeight="1">
+      <c r="A135" s="23" t="inlineStr">
+        <is>
+          <t>Luciana Elizabeth Alfonso</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>44,901,773</t>
+        </is>
+      </c>
+      <c r="C135" s="23" t="inlineStr">
+        <is>
+          <t>Lucialfonso2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr">
+        <is>
+          <t>3795-002723</t>
+        </is>
+      </c>
+      <c r="E135" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="n"/>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18.75" customHeight="1">
+      <c r="A136" s="23" t="inlineStr">
+        <is>
+          <t>Emanuel Alexia Castañeda</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>44,212,956</t>
+        </is>
+      </c>
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>emanuelcast2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>3795-182675</t>
+        </is>
+      </c>
+      <c r="E136" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="n"/>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18.75" customHeight="1">
+      <c r="A137" s="23" t="inlineStr">
+        <is>
+          <t>Berenice Correa</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>46,718,257</t>
+        </is>
+      </c>
+      <c r="C137" s="23" t="inlineStr">
+        <is>
+          <t>bereeco2901@gmail.com</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="inlineStr">
+        <is>
+          <t>3795169881</t>
+        </is>
+      </c>
+      <c r="E137" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="n"/>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18.75" customHeight="1">
+      <c r="A138" s="23" t="inlineStr">
+        <is>
+          <t>Lucas Paredes</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>46,775,141</t>
+        </is>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>luk077068@gmail.com</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>3795767307</t>
+        </is>
+      </c>
+      <c r="E138" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="n"/>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18.75" customHeight="1">
+      <c r="A139" s="23" t="inlineStr">
+        <is>
+          <t>Juan Carlos Ramirez</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>36,469,370</t>
+        </is>
+      </c>
+      <c r="C139" s="23" t="inlineStr">
+        <is>
+          <t>Juanramirezt147@gmail.com</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>3794572191</t>
+        </is>
+      </c>
+      <c r="E139" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="n"/>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18.75" customHeight="1">
+      <c r="A140" s="23" t="inlineStr">
+        <is>
+          <t>Joana Belén Pereyra</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>36,332,652</t>
+        </is>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>yoanapereyra05@gmail.com</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>3795-591789</t>
+        </is>
+      </c>
+      <c r="E140" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18.75" customHeight="1">
+      <c r="A141" s="23" t="inlineStr">
+        <is>
+          <t>Romina Alejandra Fleita</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>32,065,769</t>
+        </is>
+      </c>
+      <c r="C141" s="23" t="inlineStr">
+        <is>
+          <t>romina30303@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>3624750508</t>
+        </is>
+      </c>
+      <c r="E141" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18.75" customHeight="1">
+      <c r="A142" s="23" t="inlineStr">
+        <is>
+          <t>Isabel Catalina Monzon</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>25,387,914</t>
+        </is>
+      </c>
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t>gimenasolis50@gmail.com</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>3794697400</t>
+        </is>
+      </c>
+      <c r="E142" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia Tabernáculo Mundial de Oración (Santa Rosa, Ctes)</t>
+        </is>
+      </c>
+      <c r="F142" s="14" t="n"/>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>en espera</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18.75" customHeight="1">
+      <c r="A143" s="23" t="inlineStr">
+        <is>
+          <t>David Ramon Solis</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>23,924,888</t>
+        </is>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>gimenasolis50@gmail.com</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>3782-474313</t>
+        </is>
+      </c>
+      <c r="E143" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia Tabernáculo Mundial de Oración (Santa Rosa, Ctes)</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="n"/>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>en espera</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18.75" customHeight="1">
+      <c r="A144" s="23" t="inlineStr">
+        <is>
+          <t>Mateo Corbalán</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>34,356,757</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>mateocorbalan89@gmail.com</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>3813007522</t>
+        </is>
+      </c>
+      <c r="E144" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia Barrio Sur</t>
+        </is>
+      </c>
+      <c r="F144" s="14" t="n"/>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18.75" customHeight="1">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
+          <t>Carolina Patricia Martinez</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>36,014,506</t>
+        </is>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>martinezcarolina1933@gmail.com</t>
+        </is>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>3718568891</t>
+        </is>
+      </c>
+      <c r="E145" s="23" t="inlineStr">
+        <is>
+          <t>Más que Vencedores</t>
+        </is>
+      </c>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18.75" customHeight="1">
+      <c r="A146" s="23" t="inlineStr">
+        <is>
+          <t>Isabel María Bernarda Galarza</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>28,088,832</t>
+        </is>
+      </c>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t>isabelgalarza87@gmail.com</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>3794014630</t>
+        </is>
+      </c>
+      <c r="E146" s="23" t="n"/>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18.75" customHeight="1">
+      <c r="A147" s="23" t="inlineStr">
+        <is>
+          <t>Antonela Moreira</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>42,995,217</t>
+        </is>
+      </c>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t>antoaima003@gmail.com</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>3795368044</t>
+        </is>
+      </c>
+      <c r="E147" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F147" s="14" t="n"/>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18.75" customHeight="1">
+      <c r="A148" s="23" t="inlineStr">
+        <is>
+          <t>Elizabet Carolina Dañiluk</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>26,615,132</t>
+        </is>
+      </c>
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t>Lizy_bienestar@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>3624593699</t>
+        </is>
+      </c>
+      <c r="E148" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia de Dios</t>
+        </is>
+      </c>
+      <c r="F148" s="14" t="n"/>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18.75" customHeight="1">
+      <c r="A149" s="23" t="inlineStr">
+        <is>
+          <t>Matías Daniel Oliveira</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>41,497,391</t>
+        </is>
+      </c>
+      <c r="C149" s="23" t="inlineStr">
+        <is>
+          <t>matiasscz.98@gmail.com</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>3794040026</t>
+        </is>
+      </c>
+      <c r="E149" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F149" s="14" t="n"/>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18.75" customHeight="1">
+      <c r="A150" s="23" t="inlineStr">
+        <is>
+          <t>Antonella Beatriz Ruiz Diaz</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>42,450,788</t>
+        </is>
+      </c>
+      <c r="C150" s="23" t="inlineStr">
+        <is>
+          <t>Anthogar.info@gmail.com</t>
+        </is>
+      </c>
+      <c r="D150" s="17" t="inlineStr">
+        <is>
+          <t>3782431553</t>
+        </is>
+      </c>
+      <c r="E150" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F150" s="14" t="n"/>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18.75" customHeight="1">
+      <c r="A151" s="23" t="inlineStr">
+        <is>
+          <t>Aldo Ramon Prisco</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>36,815,953</t>
+        </is>
+      </c>
+      <c r="C151" s="23" t="inlineStr">
+        <is>
+          <t>Aldideus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>3782431553</t>
+        </is>
+      </c>
+      <c r="E151" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F151" s="14" t="n"/>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18.75" customHeight="1">
+      <c r="A152" s="23" t="inlineStr">
+        <is>
+          <t>Juan Manuel Juarez</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>16,376,139</t>
+        </is>
+      </c>
+      <c r="C152" s="23" t="inlineStr">
+        <is>
+          <t>juanmanueljuarez136@gmail.com</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr">
+        <is>
+          <t>3794766358</t>
+        </is>
+      </c>
+      <c r="E152" s="23" t="inlineStr">
+        <is>
+          <t>Casa de Oración Puerta la Hermosa</t>
+        </is>
+      </c>
+      <c r="F152" s="14" t="n"/>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18.75" customHeight="1">
+      <c r="A153" s="23" t="inlineStr">
+        <is>
+          <t>Viviana Vazquez</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>18,529,681</t>
+        </is>
+      </c>
+      <c r="C153" s="23" t="inlineStr">
+        <is>
+          <t>vivivazques@gmail.com</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
+        <is>
+          <t>3794894252</t>
+        </is>
+      </c>
+      <c r="E153" s="23" t="inlineStr">
+        <is>
+          <t>Casa de Oración Puerta la Hermosa</t>
+        </is>
+      </c>
+      <c r="F153" s="14" t="n"/>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18.75" customHeight="1">
+      <c r="A154" s="23" t="inlineStr">
+        <is>
+          <t>Juan Cruz Juarez</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>42,005,470</t>
+        </is>
+      </c>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t>juancruzjuarez19@gmail.com</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>3795007370</t>
+        </is>
+      </c>
+      <c r="E154" s="23" t="inlineStr">
+        <is>
+          <t>Casa de Oración Puerta la Hermosa</t>
+        </is>
+      </c>
+      <c r="F154" s="14" t="n"/>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18.75" customHeight="1">
+      <c r="A155" s="23" t="inlineStr">
+        <is>
+          <t>Agustina Enríquez Umeres</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>42,985,943</t>
+        </is>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t>Agus.enriquez96@gmail.com</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>3624951975</t>
+        </is>
+      </c>
+      <c r="E155" s="23" t="inlineStr">
+        <is>
+          <t>Pacto de Restauración Central</t>
+        </is>
+      </c>
+      <c r="F155" s="14" t="n"/>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18.75" customHeight="1">
+      <c r="A156" s="23" t="inlineStr">
+        <is>
+          <t>Eric Ariel Franco Abaria</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>33,683,109</t>
+        </is>
+      </c>
+      <c r="C156" s="23" t="inlineStr">
+        <is>
+          <t>ericarielfrancoabaria@gmail.com</t>
+        </is>
+      </c>
+      <c r="D156" s="17" t="inlineStr">
+        <is>
+          <t>2617751128</t>
+        </is>
+      </c>
+      <c r="E156" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F156" s="14" t="n"/>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18.75" customHeight="1">
+      <c r="A157" s="23" t="inlineStr">
+        <is>
+          <t>Sandra Noemi Vega</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>24,937,361</t>
+        </is>
+      </c>
+      <c r="C157" s="23" t="inlineStr">
+        <is>
+          <t>s.andrisv@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>3795000334</t>
+        </is>
+      </c>
+      <c r="E157" s="23" t="inlineStr">
+        <is>
+          <t>Portal del Cielo</t>
+        </is>
+      </c>
+      <c r="F157" s="14" t="n"/>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18.75" customHeight="1">
+      <c r="A158" s="23" t="inlineStr">
+        <is>
+          <t>Braian Emanuel Angel Plaza</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>45,599,069</t>
+        </is>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t>eliseo7908@gmail.com</t>
+        </is>
+      </c>
+      <c r="D158" s="17" t="inlineStr">
+        <is>
+          <t>3873584327</t>
+        </is>
+      </c>
+      <c r="E158" s="23" t="inlineStr">
+        <is>
+          <t>Somos Familia - Tartagal, Salta</t>
+        </is>
+      </c>
+      <c r="F158" s="14" t="n"/>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18.75" customHeight="1">
+      <c r="A159" s="23" t="inlineStr">
+        <is>
+          <t>Eliseo David Plaza</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>27,252,207</t>
+        </is>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>eliseo7908@gmail.com</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>3873554235</t>
+        </is>
+      </c>
+      <c r="E159" s="23" t="inlineStr">
+        <is>
+          <t>Somos Familia - Tartagal, Salta</t>
+        </is>
+      </c>
+      <c r="F159" s="14" t="n"/>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18.75" customHeight="1">
+      <c r="A160" s="23" t="inlineStr">
+        <is>
+          <t>Milton Vidal</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>34,733,825</t>
+        </is>
+      </c>
+      <c r="C160" s="23" t="inlineStr">
+        <is>
+          <t>Ulisesvidalm@gmail.com</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>3794027334</t>
+        </is>
+      </c>
+      <c r="E160" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F160" s="14" t="n"/>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18.75" customHeight="1">
+      <c r="A161" s="23" t="inlineStr">
+        <is>
+          <t>Graciela Viviana Perez</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>25,760,187</t>
+        </is>
+      </c>
+      <c r="C161" s="23" t="inlineStr">
+        <is>
+          <t>perezgrey598@gmail.com</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="n"/>
+      <c r="E161" s="23" t="n"/>
+      <c r="F161" s="14" t="n"/>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18.75" customHeight="1">
+      <c r="A162" s="23" t="inlineStr">
+        <is>
+          <t>Milagros Perez</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>50,727,050</t>
+        </is>
+      </c>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>Soldailenmilagrodperez@gmail.com</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="n"/>
+      <c r="E162" s="23" t="n"/>
+      <c r="F162" s="14" t="n"/>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18.75" customHeight="1">
+      <c r="A163" s="23" t="inlineStr">
+        <is>
+          <t>Diego Nicolas Martín</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>32,990,316</t>
+        </is>
+      </c>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>dnmartinarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="n"/>
+      <c r="E163" s="23" t="n"/>
+      <c r="F163" s="14" t="n"/>
+      <c r="G163" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18.75" customHeight="1">
+      <c r="A164" s="23" t="inlineStr">
+        <is>
+          <t>Delfor Bordon</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>32,062,931</t>
+        </is>
+      </c>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>delforisraelbordon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="n"/>
+      <c r="E164" s="23" t="n"/>
+      <c r="F164" s="14" t="n"/>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18.75" customHeight="1">
+      <c r="A165" s="23" t="inlineStr">
+        <is>
+          <t>Pablo Angel Nicolás Vargas</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>30,959,983</t>
+        </is>
+      </c>
+      <c r="C165" s="23" t="inlineStr">
+        <is>
+          <t>pablovargas2984@gmail.com</t>
+        </is>
+      </c>
+      <c r="D165" s="17" t="inlineStr">
+        <is>
+          <t>3794092697</t>
+        </is>
+      </c>
+      <c r="E165" s="23" t="inlineStr">
+        <is>
+          <t>Portal del Cielo</t>
+        </is>
+      </c>
+      <c r="F165" s="14" t="n"/>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18.75" customHeight="1">
+      <c r="A166" s="23" t="inlineStr">
+        <is>
+          <t>María Belén Martinez Merello</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>28,940,912</t>
+        </is>
+      </c>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>mbmm_05@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D166" s="17" t="inlineStr">
+        <is>
+          <t>3794006240</t>
+        </is>
+      </c>
+      <c r="E166" s="23" t="inlineStr">
+        <is>
+          <t>Portal del Cielo</t>
+        </is>
+      </c>
+      <c r="F166" s="14" t="n"/>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18.75" customHeight="1">
+      <c r="A167" s="23" t="inlineStr">
+        <is>
+          <t>Ammiel Leonardo Giaccarini</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>33,573,457</t>
+        </is>
+      </c>
+      <c r="C167" s="23" t="inlineStr">
+        <is>
+          <t>agiaccarini@gmail.com</t>
+        </is>
+      </c>
+      <c r="D167" s="17" t="inlineStr">
+        <is>
+          <t>3434800055</t>
+        </is>
+      </c>
+      <c r="E167" s="23" t="inlineStr">
+        <is>
+          <t>AdoraSion - Comunidad Entre Ríos</t>
+        </is>
+      </c>
+      <c r="F167" s="14" t="n"/>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18.75" customHeight="1">
+      <c r="A168" s="23" t="inlineStr">
+        <is>
+          <t>Delfina Eunice Galliotti</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>50,726,768</t>
+        </is>
+      </c>
+      <c r="C168" s="23" t="inlineStr">
+        <is>
+          <t>delfinagalliotti4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D168" s="17" t="inlineStr">
+        <is>
+          <t>3624631132</t>
+        </is>
+      </c>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F168" s="14" t="n"/>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18.75" customHeight="1">
+      <c r="A169" s="23" t="inlineStr">
+        <is>
+          <t>Mario Javier Galliotti</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>28,047,111</t>
+        </is>
+      </c>
+      <c r="C169" s="23" t="inlineStr">
+        <is>
+          <t>mariogalliotti457@gmail.com</t>
+        </is>
+      </c>
+      <c r="D169" s="17" t="inlineStr">
+        <is>
+          <t>3624368220</t>
+        </is>
+      </c>
+      <c r="E169" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F169" s="14" t="n"/>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18.75" customHeight="1">
+      <c r="A170" s="23" t="inlineStr">
+        <is>
+          <t>Mónica Edith Zarza</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>32,446,290</t>
+        </is>
+      </c>
+      <c r="C170" s="23" t="inlineStr">
+        <is>
+          <t>zarzaedith10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
+        <is>
+          <t>3624631132</t>
+        </is>
+      </c>
+      <c r="E170" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F170" s="14" t="n"/>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18.75" customHeight="1">
+      <c r="A171" s="23" t="inlineStr">
+        <is>
+          <t>Dalila Gonzalez Vedoya</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>38,712,428</t>
+        </is>
+      </c>
+      <c r="C171" s="23" t="inlineStr">
+        <is>
+          <t>dalilagonzalezvedoya@gmail.com</t>
+        </is>
+      </c>
+      <c r="D171" s="17" t="inlineStr">
+        <is>
+          <t>3782404436</t>
+        </is>
+      </c>
+      <c r="E171" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F171" s="14" t="n"/>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18.75" customHeight="1">
+      <c r="A172" s="23" t="inlineStr">
+        <is>
+          <t>Nelson Emmanuel Zarza</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>41,728,543</t>
+        </is>
+      </c>
+      <c r="C172" s="23" t="inlineStr">
+        <is>
+          <t>emmazarza0@gmail.com</t>
+        </is>
+      </c>
+      <c r="D172" s="17" t="inlineStr">
+        <is>
+          <t>3624237984</t>
+        </is>
+      </c>
+      <c r="E172" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F172" s="14" t="n"/>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18.75" customHeight="1">
+      <c r="A173" s="23" t="inlineStr">
+        <is>
+          <t>Mirtha Micaela Zarza</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>47,041,470</t>
+        </is>
+      </c>
+      <c r="C173" s="23" t="inlineStr">
+        <is>
+          <t>zarzamica363@gmail.com</t>
+        </is>
+      </c>
+      <c r="D173" s="17" t="inlineStr">
+        <is>
+          <t>3625692829</t>
+        </is>
+      </c>
+      <c r="E173" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F173" s="14" t="n"/>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18.75" customHeight="1">
+      <c r="A174" s="23" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Romero Gomez</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>31,102,668</t>
+        </is>
+      </c>
+      <c r="C174" s="23" t="inlineStr">
+        <is>
+          <t>Sebastiaromero84@gmail.com</t>
+        </is>
+      </c>
+      <c r="D174" s="17" t="inlineStr">
+        <is>
+          <t>1130415316</t>
+        </is>
+      </c>
+      <c r="E174" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F174" s="14" t="n"/>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18.75" customHeight="1">
+      <c r="A175" s="23" t="inlineStr">
+        <is>
+          <t>Tiziano Adrian Pasarello</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>47,615,700</t>
+        </is>
+      </c>
+      <c r="C175" s="23" t="inlineStr">
+        <is>
+          <t>Caballerojohana775@gmail.com</t>
+        </is>
+      </c>
+      <c r="D175" s="17" t="inlineStr">
+        <is>
+          <t>1154595029</t>
+        </is>
+      </c>
+      <c r="E175" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F175" s="14" t="n"/>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18.75" customHeight="1">
+      <c r="A176" s="23" t="inlineStr">
+        <is>
+          <t>Erica Natalia Cardozo</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>29,767,632</t>
+        </is>
+      </c>
+      <c r="C176" s="23" t="inlineStr">
+        <is>
+          <t>ericanataliacardozo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D176" s="17" t="inlineStr">
+        <is>
+          <t>3624642897</t>
+        </is>
+      </c>
+      <c r="E176" s="23" t="inlineStr">
+        <is>
+          <t>Casa de Dios MVI Chaco</t>
+        </is>
+      </c>
+      <c r="F176" s="14" t="n"/>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18.75" customHeight="1">
+      <c r="A177" s="23" t="inlineStr">
+        <is>
+          <t>Francisco Rodrigo Daniel Correa</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>42,987,004</t>
+        </is>
+      </c>
+      <c r="C177" s="23" t="inlineStr">
+        <is>
+          <t>ericanataliacardozo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D177" s="17" t="inlineStr">
+        <is>
+          <t>3625252230</t>
+        </is>
+      </c>
+      <c r="E177" s="23" t="inlineStr">
+        <is>
+          <t>Casa de Dios MVI Chaco</t>
+        </is>
+      </c>
+      <c r="F177" s="14" t="n"/>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18.75" customHeight="1">
+      <c r="A178" s="23" t="inlineStr">
+        <is>
+          <t>Valeria Alejandra Gómez</t>
+        </is>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>38,880,200</t>
+        </is>
+      </c>
+      <c r="C178" s="23" t="inlineStr">
+        <is>
+          <t>valeriaalejandragomez12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D178" s="17" t="inlineStr">
+        <is>
+          <t>3794283814</t>
+        </is>
+      </c>
+      <c r="E178" s="23" t="inlineStr">
+        <is>
+          <t>Yahshua Salva</t>
+        </is>
+      </c>
+      <c r="F178" s="14" t="n"/>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18.75" customHeight="1">
+      <c r="A179" s="23" t="inlineStr">
+        <is>
+          <t>Lucrecia Solange Padrón</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t>34,595,431</t>
+        </is>
+      </c>
+      <c r="C179" s="23" t="inlineStr">
+        <is>
+          <t>padronsolange@gmail.com</t>
+        </is>
+      </c>
+      <c r="D179" s="17" t="inlineStr">
+        <is>
+          <t>3704676973</t>
+        </is>
+      </c>
+      <c r="E179" s="23" t="inlineStr">
+        <is>
+          <t>Misión Evangélica Id</t>
+        </is>
+      </c>
+      <c r="F179" s="14" t="n"/>
+      <c r="G179" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18.75" customHeight="1">
+      <c r="A180" s="23" t="inlineStr">
+        <is>
+          <t>Matías Misael Piriz</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>44,332,271</t>
+        </is>
+      </c>
+      <c r="C180" s="23" t="inlineStr">
+        <is>
+          <t>Pirizmatias110@gmail.com</t>
+        </is>
+      </c>
+      <c r="D180" s="17" t="inlineStr">
+        <is>
+          <t>3624212053</t>
+        </is>
+      </c>
+      <c r="E180" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F180" s="14" t="n"/>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18.75" customHeight="1">
+      <c r="A181" s="23" t="inlineStr">
+        <is>
+          <t>Noelia Inocencia Medrano</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t>40,754,479</t>
+        </is>
+      </c>
+      <c r="C181" s="23" t="inlineStr">
+        <is>
+          <t>pirizmatias110@gmail.com</t>
+        </is>
+      </c>
+      <c r="D181" s="17" t="inlineStr">
+        <is>
+          <t>3624212048</t>
+        </is>
+      </c>
+      <c r="E181" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F181" s="14" t="n"/>
+      <c r="G181" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18.75" customHeight="1">
+      <c r="A182" s="23" t="inlineStr">
+        <is>
+          <t>Juan Manuel Medrano</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>36,972,385</t>
+        </is>
+      </c>
+      <c r="C182" s="23" t="inlineStr">
+        <is>
+          <t>medranojuanmanuel76@gmail.com</t>
+        </is>
+      </c>
+      <c r="D182" s="17" t="inlineStr">
+        <is>
+          <t>3624362173</t>
+        </is>
+      </c>
+      <c r="E182" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F182" s="14" t="n"/>
+      <c r="G182" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18.75" customHeight="1">
+      <c r="A183" s="23" t="inlineStr">
+        <is>
+          <t>Alicia Belén González</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t>39,776,074</t>
+        </is>
+      </c>
+      <c r="C183" s="23" t="inlineStr">
+        <is>
+          <t>belenalic2018@gmail.com</t>
+        </is>
+      </c>
+      <c r="D183" s="17" t="inlineStr">
+        <is>
+          <t>3624267916</t>
+        </is>
+      </c>
+      <c r="E183" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F183" s="14" t="n"/>
+      <c r="G183" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18.75" customHeight="1">
+      <c r="A184" s="23" t="inlineStr">
+        <is>
+          <t>Alejandro Emiliano Encina</t>
+        </is>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>30,705,562</t>
+        </is>
+      </c>
+      <c r="C184" s="23" t="inlineStr">
+        <is>
+          <t>aencina2417@gmail.com</t>
+        </is>
+      </c>
+      <c r="D184" s="17" t="inlineStr">
+        <is>
+          <t>3624209135</t>
+        </is>
+      </c>
+      <c r="E184" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F184" s="14" t="n"/>
+      <c r="G184" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="18.75" customHeight="1">
+      <c r="A185" s="23" t="inlineStr">
+        <is>
+          <t>Karen Yamila Piriz</t>
+        </is>
+      </c>
+      <c r="B185" s="16" t="inlineStr">
+        <is>
+          <t>37,975,296</t>
+        </is>
+      </c>
+      <c r="C185" s="23" t="inlineStr">
+        <is>
+          <t>Yamilovey166@gmail.com</t>
+        </is>
+      </c>
+      <c r="D185" s="17" t="inlineStr">
+        <is>
+          <t>3625692147</t>
+        </is>
+      </c>
+      <c r="E185" s="23" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="F185" s="14" t="n"/>
+      <c r="G185" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="18.75" customHeight="1">
+      <c r="A186" s="23" t="inlineStr">
+        <is>
+          <t>Karen Daiana Pared</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
+        <is>
+          <t>42,263,278</t>
+        </is>
+      </c>
+      <c r="C186" s="23" t="inlineStr">
+        <is>
+          <t>paredkarenestudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D186" s="17" t="inlineStr">
+        <is>
+          <t>3624159085</t>
+        </is>
+      </c>
+      <c r="E186" s="23" t="inlineStr">
+        <is>
+          <t>Pacto de Restauración</t>
+        </is>
+      </c>
+      <c r="F186" s="14" t="n"/>
+      <c r="G186" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18.75" customHeight="1">
+      <c r="A187" s="23" t="inlineStr">
+        <is>
+          <t>Mariana Elizabeth Lugo</t>
+        </is>
+      </c>
+      <c r="B187" s="16" t="inlineStr">
+        <is>
+          <t>35,439,182</t>
+        </is>
+      </c>
+      <c r="C187" s="23" t="inlineStr">
+        <is>
+          <t>marianalugo.018m@gmail.com</t>
+        </is>
+      </c>
+      <c r="D187" s="17" t="inlineStr">
+        <is>
+          <t>3794599486</t>
+        </is>
+      </c>
+      <c r="E187" s="23" t="inlineStr">
+        <is>
+          <t>Iglesia Casa de Yahweh</t>
+        </is>
+      </c>
+      <c r="F187" s="14" t="n"/>
+      <c r="G187" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18.75" customHeight="1">
+      <c r="A188" s="23" t="inlineStr">
+        <is>
+          <t>Ezequiel Vargas</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
+        <is>
+          <t>40,817,080</t>
+        </is>
+      </c>
+      <c r="C188" s="23" t="inlineStr">
+        <is>
+          <t>vargasezequiel335@gmail.com</t>
+        </is>
+      </c>
+      <c r="D188" s="17" t="inlineStr">
+        <is>
+          <t>3795007539</t>
+        </is>
+      </c>
+      <c r="E188" s="23" t="inlineStr">
+        <is>
+          <t>Elim</t>
+        </is>
+      </c>
+      <c r="F188" s="14" t="n"/>
+      <c r="G188" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18.75" customHeight="1">
+      <c r="A189" s="23" t="inlineStr">
+        <is>
+          <t>Gastón Mierke</t>
+        </is>
+      </c>
+      <c r="B189" s="16" t="inlineStr">
+        <is>
+          <t>46,962,793</t>
+        </is>
+      </c>
+      <c r="C189" s="23" t="inlineStr">
+        <is>
+          <t>Gastonmierke77@gmail.com</t>
+        </is>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
+        <is>
+          <t>3735475049</t>
+        </is>
+      </c>
+      <c r="E189" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F189" s="14" t="n"/>
+      <c r="G189" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18.75" customHeight="1">
+      <c r="A190" s="23" t="inlineStr">
+        <is>
+          <t>Yanina Rojas</t>
+        </is>
+      </c>
+      <c r="B190" s="16" t="inlineStr">
+        <is>
+          <t>38,877,198</t>
+        </is>
+      </c>
+      <c r="C190" s="23" t="inlineStr">
+        <is>
+          <t>yr6659789@gmail.com</t>
+        </is>
+      </c>
+      <c r="D190" s="17" t="inlineStr">
+        <is>
+          <t>3794754701</t>
+        </is>
+      </c>
+      <c r="E190" s="23" t="n"/>
+      <c r="F190" s="14" t="n"/>
+      <c r="G190" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18.75" customHeight="1">
+      <c r="A191" s="23" t="inlineStr">
+        <is>
+          <t>Erica Vallejos</t>
+        </is>
+      </c>
+      <c r="B191" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C191" s="23" t="n"/>
+      <c r="D191" s="17" t="inlineStr">
+        <is>
+          <t>3794804379</t>
+        </is>
+      </c>
+      <c r="E191" s="23" t="inlineStr">
+        <is>
+          <t>Elim</t>
+        </is>
+      </c>
+      <c r="F191" s="14" t="n"/>
+      <c r="G191" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="18.75" customHeight="1">
+      <c r="A192" s="23" t="inlineStr">
+        <is>
+          <t>Esteban Sivisstum</t>
+        </is>
+      </c>
+      <c r="B192" s="16" t="inlineStr">
+        <is>
+          <t>46,862,085</t>
+        </is>
+      </c>
+      <c r="C192" s="23" t="n"/>
+      <c r="D192" s="17" t="inlineStr">
+        <is>
+          <t>3794928364</t>
+        </is>
+      </c>
+      <c r="E192" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F192" s="14" t="n"/>
+      <c r="G192" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="18.75" customHeight="1">
+      <c r="A193" s="23" t="inlineStr">
+        <is>
+          <t>Martin Mena</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="inlineStr">
+        <is>
+          <t>21,772,355</t>
+        </is>
+      </c>
+      <c r="C193" s="23" t="n"/>
+      <c r="D193" s="17" t="inlineStr">
+        <is>
+          <t>56997115251</t>
+        </is>
+      </c>
+      <c r="E193" s="23" t="n"/>
+      <c r="F193" s="14" t="n"/>
+      <c r="G193" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18.75" customHeight="1">
+      <c r="A194" s="23" t="inlineStr">
+        <is>
+          <t>Melisa</t>
+        </is>
+      </c>
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C194" s="23" t="n"/>
+      <c r="D194" s="17" t="inlineStr">
+        <is>
+          <t>3794786725</t>
+        </is>
+      </c>
+      <c r="E194" s="23" t="n"/>
+      <c r="F194" s="14" t="n"/>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18.75" customHeight="1">
+      <c r="A195" s="23" t="inlineStr">
+        <is>
+          <t>Emiliano</t>
+        </is>
+      </c>
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C195" s="23" t="n"/>
+      <c r="D195" s="17" t="inlineStr">
+        <is>
+          <t>3794258889</t>
+        </is>
+      </c>
+      <c r="E195" s="23" t="n"/>
+      <c r="F195" s="14" t="n"/>
+      <c r="G195" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="18.75" customHeight="1">
+      <c r="A196" s="23" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C196" s="23" t="n"/>
+      <c r="D196" s="17" t="inlineStr">
+        <is>
+          <t>3795115187</t>
+        </is>
+      </c>
+      <c r="E196" s="23" t="n"/>
+      <c r="F196" s="14" t="n"/>
+      <c r="G196" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="18.75" customHeight="1">
+      <c r="A197" s="23" t="inlineStr">
+        <is>
+          <t>Dani</t>
+        </is>
+      </c>
+      <c r="B197" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C197" s="23" t="n"/>
+      <c r="D197" s="17" t="inlineStr">
+        <is>
+          <t>3795382796</t>
+        </is>
+      </c>
+      <c r="E197" s="23" t="n"/>
+      <c r="F197" s="14" t="n"/>
+      <c r="G197" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="18.75" customHeight="1">
+      <c r="A198" s="23" t="inlineStr">
+        <is>
+          <t>Maca</t>
+        </is>
+      </c>
+      <c r="B198" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C198" s="23" t="n"/>
+      <c r="D198" s="17" t="inlineStr">
+        <is>
+          <t>3794045157</t>
+        </is>
+      </c>
+      <c r="E198" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F198" s="14" t="n"/>
+      <c r="G198" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18.75" customHeight="1">
+      <c r="A199" s="23" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="B199" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C199" s="23" t="n"/>
+      <c r="D199" s="17" t="inlineStr">
+        <is>
+          <t>3794927171</t>
+        </is>
+      </c>
+      <c r="E199" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F199" s="14" t="n"/>
+      <c r="G199" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18.75" customHeight="1">
+      <c r="A200" s="23" t="inlineStr">
+        <is>
+          <t>Ricardo Cuaranta</t>
+        </is>
+      </c>
+      <c r="B200" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C200" s="23" t="n"/>
+      <c r="D200" s="17" t="inlineStr">
+        <is>
+          <t>3794201155</t>
+        </is>
+      </c>
+      <c r="E200" s="23" t="n"/>
+      <c r="F200" s="14" t="n"/>
+      <c r="G200" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18.75" customHeight="1">
+      <c r="A201" s="23" t="inlineStr">
+        <is>
+          <t>Norma Cuaranta</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C201" s="23" t="n"/>
+      <c r="D201" s="17" t="inlineStr">
+        <is>
+          <t>3795037113</t>
+        </is>
+      </c>
+      <c r="E201" s="23" t="n"/>
+      <c r="F201" s="14" t="n"/>
+      <c r="G201" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18.75" customHeight="1">
+      <c r="A202" s="23" t="inlineStr">
+        <is>
+          <t>Karen Cuaranta</t>
+        </is>
+      </c>
+      <c r="B202" s="16" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="C202" s="23" t="n"/>
+      <c r="D202" s="17" t="inlineStr">
+        <is>
+          <t>3795204717</t>
+        </is>
+      </c>
+      <c r="E202" s="23" t="n"/>
+      <c r="F202" s="14" t="n"/>
+      <c r="G202" s="18" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18.75" customHeight="1">
+      <c r="A203" s="23" t="inlineStr">
+        <is>
+          <t>Maximiliano Samuel Tomás</t>
+        </is>
+      </c>
+      <c r="B203" s="24" t="inlineStr">
+        <is>
+          <t>45,456,956</t>
+        </is>
+      </c>
+      <c r="C203" s="23" t="inlineStr">
+        <is>
+          <t>maximilianotomas2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="D203" s="25" t="inlineStr">
+        <is>
+          <t>3777205769</t>
+        </is>
+      </c>
+      <c r="E203" s="23" t="inlineStr">
+        <is>
+          <t>Vida Nueva</t>
+        </is>
+      </c>
+      <c r="F203" s="26" t="n"/>
+      <c r="G203" s="18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="18.75" customHeight="1">
+      <c r="A204" s="23" t="inlineStr">
+        <is>
+          <t>Fabricio Nahuel Ojeda</t>
+        </is>
+      </c>
+      <c r="B204" s="24" t="inlineStr">
+        <is>
+          <t>46,254,433</t>
+        </is>
+      </c>
+      <c r="C204" s="23" t="inlineStr">
+        <is>
+          <t>Fabrinau2005@gmail.com</t>
+        </is>
+      </c>
+      <c r="D204" s="25" t="inlineStr">
+        <is>
+          <t>3711412301</t>
+        </is>
+      </c>
+      <c r="E204" s="23" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="F204" s="26" t="n"/>
+      <c r="G204" s="27" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>

--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -545,8 +545,8 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G204"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G208"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.005" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
     <col width="25.005" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="B202" s="16" t="inlineStr">
         <is>
-          <t>11,111,111</t>
+          <t>39,187,499</t>
         </is>
       </c>
       <c r="C202" s="23" t="n"/>
@@ -7135,11 +7135,15 @@
           <t>3795204717</t>
         </is>
       </c>
-      <c r="E202" s="23" t="n"/>
+      <c r="E202" s="23" t="inlineStr">
+        <is>
+          <t>TMA Sta Rosa Ctes</t>
+        </is>
+      </c>
       <c r="F202" s="14" t="n"/>
       <c r="G202" s="18" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>enviado</t>
         </is>
       </c>
     </row>
@@ -7204,6 +7208,124 @@
       </c>
       <c r="F204" s="26" t="n"/>
       <c r="G204" s="27" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Martin Luis Báez</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>30,424,212</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>baezluismartin1983@gmail.com</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>3794329052</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Mónica Gisele Encina</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>29,379,636</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>monimonisweety@gmail.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>3794865580</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Alfredo Ramírez</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>47,716,254</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0984204524</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Ministerio Despertando Un Avivamiento</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Jael Matto</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>6,207,023</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0984204524</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Ministerio Despertando Un Avivamiento</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>

--- a/data/asistentes.xlsx
+++ b/data/asistentes.xlsx
@@ -545,8 +545,8 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G226"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25.005" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
     <col width="25.005" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
@@ -7331,6 +7331,547 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Claudio Roberto Emanuel Ugarte</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>38,340,847</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Emanuelugarte0194@gmail.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>3873416131</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Somos familia</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Natalia Carolina Chavez</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>38,507,333</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Emanuelugarte0194@gmail.com</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>3873416131</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Somos familia</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Cayo Noemí Hortencia</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>28,050,484</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Emanuelugarte0194@gmail.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>3873416131</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Somos familia</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Alejandro Pérez</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>42,294,783</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>aleplineas@gmail.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>3487510120</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Una línea abierta a la vida</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Rocio Santa Cruz</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>44,165,005</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>rocio.santacruz1518@gmail.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>1173670424</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Una línea abierta a la vida</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Vannya Amira Matto</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>7,104,109</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>+595984204524</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Ministerio Despertando Un Avivamiento</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sartori Leticia Ainara</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>46,713,018</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ainaraleticia14@gmail.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>3757684970</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Thiara Mailen Preste</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>45,022,931</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>thiarapreste@gmail.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>3777690515</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Ruth Marianela Pérez</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>46,066,462</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ruthmarianela18perez@gmail.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>3715405627</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sivisstum Marcos Abiel</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>43,068,555</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>abiel5153@gmail.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>3795052745</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Timoteo Fernandez</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>30,997,708</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>3794353887</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Paola Silvero</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>3795063779</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Gaston Romero</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>3795154614</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Barbara Lacour</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>3794407928</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Lucas Santa Cruz</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>11,111,111</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>3794918986</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>VQC</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Maria Malarino</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>24,478,774</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Majonaro_96_03@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>3487644826</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Una línea abierta a la vida</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Lautaro Martin Varela Gomez</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>49,491,673</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>lautarovarela1808@gmail.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>3794664563</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Casa de Dios Ángeles del Puente</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Tiago Nahuel Silva</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>47,325,311</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>3644571194</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Conexión</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
